--- a/документы/сметы/смета-Миля-9.xlsx
+++ b/документы/сметы/смета-Миля-9.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K110"/>
+  <dimension ref="A1:K148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -645,11 +645,11 @@
         </is>
       </c>
       <c r="C7" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B7,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B7,Узлы!$A$2:$A$85,0))</f>
         <v>Демонтаж участков перегородок и вырезка проёмов 800/900 (кирпич/блок ~140 мм)</v>
       </c>
       <c r="D7" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B7,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B7,Узлы!$A$2:$A$85,0))</f>
         <v>м²</v>
       </c>
       <c r="E7" s="8">
@@ -657,11 +657,11 @@
         <v>6.5457</v>
       </c>
       <c r="F7" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B7,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B7,Узлы!$A$2:$A$85,0))</f>
         <v>14.0</v>
       </c>
       <c r="G7" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B7,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B7,Узлы!$A$2:$A$85,0))</f>
         <v>0.0</v>
       </c>
       <c r="H7" s="9">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C8" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B8,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B8,Узлы!$A$2:$A$85,0))</f>
         <v>Демонтаж радиаторов</v>
       </c>
       <c r="D8" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B8,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B8,Узлы!$A$2:$A$85,0))</f>
         <v>шт</v>
       </c>
       <c r="E8" s="11" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B8,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B8,Узлы!$A$2:$A$85,0))</f>
         <v>30.0</v>
       </c>
       <c r="G8" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B8,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B8,Узлы!$A$2:$A$85,0))</f>
         <v>0.0</v>
       </c>
       <c r="H8" s="9">
@@ -738,22 +738,22 @@
         </is>
       </c>
       <c r="C9" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B9,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B9,Узлы!$A$2:$A$85,0))</f>
         <v>Демонтаж эл. щитка с переносом (ниша в стене h=1500)</v>
       </c>
       <c r="D9" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B9,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B9,Узлы!$A$2:$A$85,0))</f>
         <v>шт</v>
       </c>
       <c r="E9" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B9,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B9,Узлы!$A$2:$A$85,0))</f>
         <v>150.0</v>
       </c>
       <c r="G9" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B9,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B9,Узлы!$A$2:$A$85,0))</f>
         <v>30.0</v>
       </c>
       <c r="H9" s="9">
@@ -784,22 +784,22 @@
         </is>
       </c>
       <c r="C10" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B10,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B10,Узлы!$A$2:$A$85,0))</f>
         <v>Вынос мусора, мешок</v>
       </c>
       <c r="D10" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B10,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B10,Узлы!$A$2:$A$85,0))</f>
         <v>мешок</v>
       </c>
       <c r="E10" s="11" t="n">
         <v>60</v>
       </c>
       <c r="F10" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B10,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B10,Узлы!$A$2:$A$85,0))</f>
         <v>2.0</v>
       </c>
       <c r="G10" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B10,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B10,Узлы!$A$2:$A$85,0))</f>
         <v>0.7</v>
       </c>
       <c r="H10" s="9">
@@ -830,22 +830,22 @@
         </is>
       </c>
       <c r="C11" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B11,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B11,Узлы!$A$2:$A$85,0))</f>
         <v>Контейнер 8 м³ / Газель</v>
       </c>
       <c r="D11" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B11,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B11,Узлы!$A$2:$A$85,0))</f>
         <v>рейс</v>
       </c>
       <c r="E11" s="11" t="n">
         <v>2</v>
       </c>
       <c r="F11" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B11,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B11,Узлы!$A$2:$A$85,0))</f>
         <v>180.0</v>
       </c>
       <c r="G11" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B11,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B11,Узлы!$A$2:$A$85,0))</f>
         <v>0.0</v>
       </c>
       <c r="H11" s="9">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="C15" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B15,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B15,Узлы!$A$2:$A$85,0))</f>
         <v>Перегородка керамзитобетон 120 мм</v>
       </c>
       <c r="D15" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B15,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B15,Узлы!$A$2:$A$85,0))</f>
         <v>м²</v>
       </c>
       <c r="E15" s="8">
@@ -924,11 +924,11 @@
         <v>5.5</v>
       </c>
       <c r="F15" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B15,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B15,Узлы!$A$2:$A$85,0))</f>
         <v>36.0</v>
       </c>
       <c r="G15" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B15,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B15,Узлы!$A$2:$A$85,0))</f>
         <v>44.0</v>
       </c>
       <c r="H15" s="9">
@@ -959,11 +959,11 @@
         </is>
       </c>
       <c r="C16" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B16,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B16,Узлы!$A$2:$A$85,0))</f>
         <v>Перегородка керамзитобетон 100 мм</v>
       </c>
       <c r="D16" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B16,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B16,Узлы!$A$2:$A$85,0))</f>
         <v>м²</v>
       </c>
       <c r="E16" s="8">
@@ -971,11 +971,11 @@
         <v>11.67</v>
       </c>
       <c r="F16" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B16,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B16,Узлы!$A$2:$A$85,0))</f>
         <v>36.0</v>
       </c>
       <c r="G16" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B16,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B16,Узлы!$A$2:$A$85,0))</f>
         <v>38.0</v>
       </c>
       <c r="H16" s="9">
@@ -1006,22 +1006,22 @@
         </is>
       </c>
       <c r="C17" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B17,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B17,Узлы!$A$2:$A$85,0))</f>
         <v>Перемычка над проёмом 900 в новой перегородке</v>
       </c>
       <c r="D17" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B17,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B17,Узлы!$A$2:$A$85,0))</f>
         <v>шт</v>
       </c>
       <c r="E17" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B17,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B17,Узлы!$A$2:$A$85,0))</f>
         <v>60.0</v>
       </c>
       <c r="G17" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B17,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B17,Узлы!$A$2:$A$85,0))</f>
         <v>40.0</v>
       </c>
       <c r="H17" s="9">
@@ -1052,22 +1052,22 @@
         </is>
       </c>
       <c r="C18" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B18,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B18,Узлы!$A$2:$A$85,0))</f>
         <v>Короб ГКЛВ инсталляции h=1200 и зашивки стояков</v>
       </c>
       <c r="D18" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B18,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B18,Узлы!$A$2:$A$85,0))</f>
         <v>м.п.</v>
       </c>
       <c r="E18" s="11" t="n">
         <v>3</v>
       </c>
       <c r="F18" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B18,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B18,Узлы!$A$2:$A$85,0))</f>
         <v>160.0</v>
       </c>
       <c r="G18" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B18,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B18,Узлы!$A$2:$A$85,0))</f>
         <v>45.0</v>
       </c>
       <c r="H18" s="9">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="C19" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B19,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B19,Узлы!$A$2:$A$85,0))</f>
         <v>Люк ревизионный скрытый под плитку/микроцемент</v>
       </c>
       <c r="D19" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B19,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B19,Узлы!$A$2:$A$85,0))</f>
         <v>шт</v>
       </c>
       <c r="E19" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B19,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B19,Узлы!$A$2:$A$85,0))</f>
         <v>110.0</v>
       </c>
       <c r="G19" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B19,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B19,Узлы!$A$2:$A$85,0))</f>
         <v>120.0</v>
       </c>
       <c r="H19" s="9">
@@ -1180,11 +1180,11 @@
         </is>
       </c>
       <c r="C23" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B23,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B23,Узлы!$A$2:$A$85,0))</f>
         <v>Штукатурка гипсовая по маякам 15 мм — ТОЛЬКО новые перегородки (обе стороны)</v>
       </c>
       <c r="D23" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B23,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B23,Узлы!$A$2:$A$85,0))</f>
         <v>м²</v>
       </c>
       <c r="E23" s="8">
@@ -1192,11 +1192,11 @@
         <v>32.45</v>
       </c>
       <c r="F23" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B23,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B23,Узлы!$A$2:$A$85,0))</f>
         <v>20.0</v>
       </c>
       <c r="G23" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B23,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B23,Узлы!$A$2:$A$85,0))</f>
         <v>9.5</v>
       </c>
       <c r="H23" s="9">
@@ -1227,11 +1227,11 @@
         </is>
       </c>
       <c r="C24" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B24,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B24,Узлы!$A$2:$A$85,0))</f>
         <v>Откосы окон и балконной двери: штукатурка + шпаклёвка + покраска</v>
       </c>
       <c r="D24" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B24,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B24,Узлы!$A$2:$A$85,0))</f>
         <v>м.п.</v>
       </c>
       <c r="E24" s="8">
@@ -1239,11 +1239,11 @@
         <v>20.0</v>
       </c>
       <c r="F24" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B24,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B24,Узлы!$A$2:$A$85,0))</f>
         <v>45.0</v>
       </c>
       <c r="G24" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B24,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B24,Узлы!$A$2:$A$85,0))</f>
         <v>8.0</v>
       </c>
       <c r="H24" s="9">
@@ -1274,11 +1274,11 @@
         </is>
       </c>
       <c r="C25" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B25,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B25,Узлы!$A$2:$A$85,0))</f>
         <v>Шпаклёвка Q3 по существующим стенам под покраску и декоративную штукатурку</v>
       </c>
       <c r="D25" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B25,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B25,Узлы!$A$2:$A$85,0))</f>
         <v>м²</v>
       </c>
       <c r="E25" s="8">
@@ -1286,11 +1286,11 @@
         <v>111.0</v>
       </c>
       <c r="F25" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B25,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B25,Узлы!$A$2:$A$85,0))</f>
         <v>30.0</v>
       </c>
       <c r="G25" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B25,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B25,Узлы!$A$2:$A$85,0))</f>
         <v>8.3</v>
       </c>
       <c r="H25" s="9">
@@ -1321,11 +1321,11 @@
         </is>
       </c>
       <c r="C26" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B26,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B26,Узлы!$A$2:$A$85,0))</f>
         <v>Стеклохолст 40 г/м² на клей (под покраску и Marmorino)</v>
       </c>
       <c r="D26" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B26,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B26,Узлы!$A$2:$A$85,0))</f>
         <v>м²</v>
       </c>
       <c r="E26" s="8">
@@ -1333,11 +1333,11 @@
         <v>111.0</v>
       </c>
       <c r="F26" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B26,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B26,Узлы!$A$2:$A$85,0))</f>
         <v>9.0</v>
       </c>
       <c r="G26" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B26,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B26,Узлы!$A$2:$A$85,0))</f>
         <v>3.2</v>
       </c>
       <c r="H26" s="9">
@@ -1368,11 +1368,11 @@
         </is>
       </c>
       <c r="C27" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B27,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B27,Узлы!$A$2:$A$85,0))</f>
         <v>Шпаклёвка Q2 под обои и фотообои</v>
       </c>
       <c r="D27" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B27,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B27,Узлы!$A$2:$A$85,0))</f>
         <v>м²</v>
       </c>
       <c r="E27" s="8">
@@ -1380,11 +1380,11 @@
         <v>40.95</v>
       </c>
       <c r="F27" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B27,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B27,Узлы!$A$2:$A$85,0))</f>
         <v>14.0</v>
       </c>
       <c r="G27" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B27,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B27,Узлы!$A$2:$A$85,0))</f>
         <v>3.0</v>
       </c>
       <c r="H27" s="9">
@@ -1415,11 +1415,11 @@
         </is>
       </c>
       <c r="C28" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B28,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B28,Узлы!$A$2:$A$85,0))</f>
         <v>Подготовка стен санузла под микроцемент (цементная шпаклёвка Q3 + грунт)</v>
       </c>
       <c r="D28" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B28,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B28,Узлы!$A$2:$A$85,0))</f>
         <v>м²</v>
       </c>
       <c r="E28" s="8">
@@ -1427,11 +1427,11 @@
         <v>18.0</v>
       </c>
       <c r="F28" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B28,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B28,Узлы!$A$2:$A$85,0))</f>
         <v>30.0</v>
       </c>
       <c r="G28" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B28,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B28,Узлы!$A$2:$A$85,0))</f>
         <v>4.5</v>
       </c>
       <c r="H28" s="9">
@@ -1498,11 +1498,11 @@
         </is>
       </c>
       <c r="C32" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B32,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B32,Узлы!$A$2:$A$85,0))</f>
         <v>Подготовка существующей стяжки: шлифовка, пылесос, ремонт трещин, CM-тест</v>
       </c>
       <c r="D32" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B32,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B32,Узлы!$A$2:$A$85,0))</f>
         <v>м²</v>
       </c>
       <c r="E32" s="8">
@@ -1510,11 +1510,11 @@
         <v>49.0</v>
       </c>
       <c r="F32" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B32,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B32,Узлы!$A$2:$A$85,0))</f>
         <v>4.0</v>
       </c>
       <c r="G32" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B32,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B32,Узлы!$A$2:$A$85,0))</f>
         <v>0.5</v>
       </c>
       <c r="H32" s="9">
@@ -1545,11 +1545,11 @@
         </is>
       </c>
       <c r="C33" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B33,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B33,Узлы!$A$2:$A$85,0))</f>
         <v>Самонивелир 10 мм с грунтом ×2 и демпфером (по проекту, лист 14 узел V1)</v>
       </c>
       <c r="D33" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B33,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B33,Узлы!$A$2:$A$85,0))</f>
         <v>м²</v>
       </c>
       <c r="E33" s="8">
@@ -1557,11 +1557,11 @@
         <v>49.0</v>
       </c>
       <c r="F33" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B33,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B33,Узлы!$A$2:$A$85,0))</f>
         <v>18.0</v>
       </c>
       <c r="G33" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B33,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B33,Узлы!$A$2:$A$85,0))</f>
         <v>15.6</v>
       </c>
       <c r="H33" s="9">
@@ -1592,11 +1592,11 @@
         </is>
       </c>
       <c r="C34" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B34,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B34,Узлы!$A$2:$A$85,0))</f>
         <v>Клеевой винил Quick-Step Pristine, палуба (запас 7 %)</v>
       </c>
       <c r="D34" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B34,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B34,Узлы!$A$2:$A$85,0))</f>
         <v>м²</v>
       </c>
       <c r="E34" s="8">
@@ -1604,11 +1604,11 @@
         <v>49.0</v>
       </c>
       <c r="F34" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B34,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B34,Узлы!$A$2:$A$85,0))</f>
         <v>30.0</v>
       </c>
       <c r="G34" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B34,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B34,Узлы!$A$2:$A$85,0))</f>
         <v>62.0</v>
       </c>
       <c r="H34" s="9">
@@ -1639,11 +1639,11 @@
         </is>
       </c>
       <c r="C35" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B35,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B35,Узлы!$A$2:$A$85,0))</f>
         <v>Керамогранит на пол санузла Argenta Westone 120×60</v>
       </c>
       <c r="D35" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B35,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B35,Узлы!$A$2:$A$85,0))</f>
         <v>м²</v>
       </c>
       <c r="E35" s="8">
@@ -1651,11 +1651,11 @@
         <v>4.78</v>
       </c>
       <c r="F35" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B35,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B35,Узлы!$A$2:$A$85,0))</f>
         <v>65.0</v>
       </c>
       <c r="G35" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B35,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B35,Узлы!$A$2:$A$85,0))</f>
         <v>160.0</v>
       </c>
       <c r="H35" s="9">
@@ -1686,11 +1686,11 @@
         </is>
       </c>
       <c r="C36" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B36,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B36,Узлы!$A$2:$A$85,0))</f>
         <v>Керамогранит у входа Ponza Lilly 200×200 (50 шт)</v>
       </c>
       <c r="D36" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B36,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B36,Узлы!$A$2:$A$85,0))</f>
         <v>м²</v>
       </c>
       <c r="E36" s="8">
@@ -1698,11 +1698,11 @@
         <v>2.0</v>
       </c>
       <c r="F36" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B36,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B36,Узлы!$A$2:$A$85,0))</f>
         <v>45.0</v>
       </c>
       <c r="G36" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B36,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B36,Узлы!$A$2:$A$85,0))</f>
         <v>71.0</v>
       </c>
       <c r="H36" s="9">
@@ -1733,11 +1733,11 @@
         </is>
       </c>
       <c r="C37" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B37,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B37,Узлы!$A$2:$A$85,0))</f>
         <v>Гидроизоляция санузла обмазочная 2 слоя (пол + стены 300 мм + душевая зона)</v>
       </c>
       <c r="D37" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B37,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B37,Узлы!$A$2:$A$85,0))</f>
         <v>м²</v>
       </c>
       <c r="E37" s="8">
@@ -1745,11 +1745,11 @@
         <v>13.08</v>
       </c>
       <c r="F37" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B37,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B37,Узлы!$A$2:$A$85,0))</f>
         <v>10.0</v>
       </c>
       <c r="G37" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B37,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B37,Узлы!$A$2:$A$85,0))</f>
         <v>8.5</v>
       </c>
       <c r="H37" s="9">
@@ -1780,11 +1780,11 @@
         </is>
       </c>
       <c r="C38" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B38,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B38,Узлы!$A$2:$A$85,0))</f>
         <v>Тёплый пол электрический Nexans (кабель в санузле и прихожей)</v>
       </c>
       <c r="D38" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B38,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B38,Узлы!$A$2:$A$85,0))</f>
         <v>м²</v>
       </c>
       <c r="E38" s="8">
@@ -1792,11 +1792,11 @@
         <v>2.77</v>
       </c>
       <c r="F38" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B38,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B38,Узлы!$A$2:$A$85,0))</f>
         <v>44.0</v>
       </c>
       <c r="G38" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B38,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B38,Узлы!$A$2:$A$85,0))</f>
         <v>90.0</v>
       </c>
       <c r="H38" s="9">
@@ -1827,22 +1827,22 @@
         </is>
       </c>
       <c r="C39" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B39,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B39,Узлы!$A$2:$A$85,0))</f>
         <v>Терморегулятор</v>
       </c>
       <c r="D39" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B39,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B39,Узлы!$A$2:$A$85,0))</f>
         <v>шт</v>
       </c>
       <c r="E39" s="11" t="n">
         <v>2</v>
       </c>
       <c r="F39" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B39,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B39,Узлы!$A$2:$A$85,0))</f>
         <v>50.0</v>
       </c>
       <c r="G39" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B39,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B39,Узлы!$A$2:$A$85,0))</f>
         <v>72.0</v>
       </c>
       <c r="H39" s="9">
@@ -1873,11 +1873,11 @@
         </is>
       </c>
       <c r="C40" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B40,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B40,Узлы!$A$2:$A$85,0))</f>
         <v>Плинтус МДФ OHZ HM-1540</v>
       </c>
       <c r="D40" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B40,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B40,Узлы!$A$2:$A$85,0))</f>
         <v>м.п.</v>
       </c>
       <c r="E40" s="8">
@@ -1885,11 +1885,11 @@
         <v>35.19</v>
       </c>
       <c r="F40" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B40,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B40,Узлы!$A$2:$A$85,0))</f>
         <v>19.0</v>
       </c>
       <c r="G40" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B40,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B40,Узлы!$A$2:$A$85,0))</f>
         <v>4.5</v>
       </c>
       <c r="H40" s="9">
@@ -1920,22 +1920,22 @@
         </is>
       </c>
       <c r="C41" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B41,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B41,Узлы!$A$2:$A$85,0))</f>
         <v>Порожки / стык LVT–керамогранит через герметик</v>
       </c>
       <c r="D41" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B41,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B41,Узлы!$A$2:$A$85,0))</f>
         <v>шт</v>
       </c>
       <c r="E41" s="11" t="n">
         <v>5</v>
       </c>
       <c r="F41" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B41,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B41,Узлы!$A$2:$A$85,0))</f>
         <v>25.0</v>
       </c>
       <c r="G41" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B41,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B41,Узлы!$A$2:$A$85,0))</f>
         <v>28.0</v>
       </c>
       <c r="H41" s="9">
@@ -2002,11 +2002,11 @@
         </is>
       </c>
       <c r="C45" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B45,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B45,Узлы!$A$2:$A$85,0))</f>
         <v>Натяжной потолок ПВХ матовый, с материалом и монтажом</v>
       </c>
       <c r="D45" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B45,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B45,Узлы!$A$2:$A$85,0))</f>
         <v>м²</v>
       </c>
       <c r="E45" s="8">
@@ -2014,11 +2014,11 @@
         <v>45.0</v>
       </c>
       <c r="F45" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B45,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B45,Узлы!$A$2:$A$85,0))</f>
         <v>28.0</v>
       </c>
       <c r="G45" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B45,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B45,Узлы!$A$2:$A$85,0))</f>
         <v>0.0</v>
       </c>
       <c r="H45" s="9">
@@ -2049,11 +2049,11 @@
         </is>
       </c>
       <c r="C46" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B46,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B46,Узлы!$A$2:$A$85,0))</f>
         <v>Теневой профиль EuroLumFer 02 по периметру</v>
       </c>
       <c r="D46" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B46,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B46,Узлы!$A$2:$A$85,0))</f>
         <v>м.п.</v>
       </c>
       <c r="E46" s="8">
@@ -2061,11 +2061,11 @@
         <v>58.0</v>
       </c>
       <c r="F46" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B46,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B46,Узлы!$A$2:$A$85,0))</f>
         <v>21.0</v>
       </c>
       <c r="G46" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B46,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B46,Узлы!$A$2:$A$85,0))</f>
         <v>0.0</v>
       </c>
       <c r="H46" s="9">
@@ -2096,11 +2096,11 @@
         </is>
       </c>
       <c r="C47" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B47,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B47,Узлы!$A$2:$A$85,0))</f>
         <v>Карнизная ниша LumFer SK Magnum / Levium / Volat</v>
       </c>
       <c r="D47" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B47,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B47,Узлы!$A$2:$A$85,0))</f>
         <v>м.п.</v>
       </c>
       <c r="E47" s="8">
@@ -2108,11 +2108,11 @@
         <v>9.0</v>
       </c>
       <c r="F47" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B47,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B47,Узлы!$A$2:$A$85,0))</f>
         <v>40.0</v>
       </c>
       <c r="G47" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B47,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B47,Узлы!$A$2:$A$85,0))</f>
         <v>35.0</v>
       </c>
       <c r="H47" s="9">
@@ -2143,22 +2143,22 @@
         </is>
       </c>
       <c r="C48" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B48,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B48,Узлы!$A$2:$A$85,0))</f>
         <v>Закладные под светильники и вент. решётку</v>
       </c>
       <c r="D48" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B48,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B48,Узлы!$A$2:$A$85,0))</f>
         <v>шт</v>
       </c>
       <c r="E48" s="11" t="n">
         <v>55</v>
       </c>
       <c r="F48" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B48,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B48,Узлы!$A$2:$A$85,0))</f>
         <v>16.0</v>
       </c>
       <c r="G48" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B48,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B48,Узлы!$A$2:$A$85,0))</f>
         <v>5.0</v>
       </c>
       <c r="H48" s="9">
@@ -2225,11 +2225,11 @@
         </is>
       </c>
       <c r="C52" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B52,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B52,Узлы!$A$2:$A$85,0))</f>
         <v>Окраска стен MAV Flagman 35, 2 слоя + грунт (УСЛ-1)</v>
       </c>
       <c r="D52" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B52,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B52,Узлы!$A$2:$A$85,0))</f>
         <v>м²</v>
       </c>
       <c r="E52" s="8">
@@ -2237,11 +2237,11 @@
         <v>50.0</v>
       </c>
       <c r="F52" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B52,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B52,Узлы!$A$2:$A$85,0))</f>
         <v>10.0</v>
       </c>
       <c r="G52" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B52,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B52,Узлы!$A$2:$A$85,0))</f>
         <v>6.0</v>
       </c>
       <c r="H52" s="9">
@@ -2272,11 +2272,11 @@
         </is>
       </c>
       <c r="C53" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B53,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B53,Узлы!$A$2:$A$85,0))</f>
         <v>Декоративная штукатурка Marmorino Naturale Fine (ДК-1), 2–3 слоя с железнением</v>
       </c>
       <c r="D53" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B53,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B53,Узлы!$A$2:$A$85,0))</f>
         <v>м²</v>
       </c>
       <c r="E53" s="8">
@@ -2284,11 +2284,11 @@
         <v>61.0</v>
       </c>
       <c r="F53" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B53,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B53,Узлы!$A$2:$A$85,0))</f>
         <v>70.0</v>
       </c>
       <c r="G53" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B53,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B53,Узлы!$A$2:$A$85,0))</f>
         <v>21.0</v>
       </c>
       <c r="H53" s="9">
@@ -2319,11 +2319,11 @@
         </is>
       </c>
       <c r="C54" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B54,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B54,Узлы!$A$2:$A$85,0))</f>
         <v>Обои Grandeco Keen KE1006 (ОБ-1)</v>
       </c>
       <c r="D54" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B54,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B54,Узлы!$A$2:$A$85,0))</f>
         <v>м²</v>
       </c>
       <c r="E54" s="8">
@@ -2331,11 +2331,11 @@
         <v>23.5</v>
       </c>
       <c r="F54" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B54,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B54,Узлы!$A$2:$A$85,0))</f>
         <v>10.0</v>
       </c>
       <c r="G54" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B54,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B54,Узлы!$A$2:$A$85,0))</f>
         <v>21.0</v>
       </c>
       <c r="H54" s="9">
@@ -2366,11 +2366,11 @@
         </is>
       </c>
       <c r="C55" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B55,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B55,Узлы!$A$2:$A$85,0))</f>
         <v>Фотообои Vinni.by (ФО-1, ФО-2)</v>
       </c>
       <c r="D55" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B55,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B55,Узлы!$A$2:$A$85,0))</f>
         <v>м²</v>
       </c>
       <c r="E55" s="8">
@@ -2378,11 +2378,11 @@
         <v>17.45</v>
       </c>
       <c r="F55" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B55,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B55,Узлы!$A$2:$A$85,0))</f>
         <v>15.0</v>
       </c>
       <c r="G55" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B55,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B55,Узлы!$A$2:$A$85,0))</f>
         <v>45.0</v>
       </c>
       <c r="H55" s="9">
@@ -2413,11 +2413,11 @@
         </is>
       </c>
       <c r="C56" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B56,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B56,Узлы!$A$2:$A$85,0))</f>
         <v>Плитка Tribeca Sage Green 6×24,6 на стены (PL-1)</v>
       </c>
       <c r="D56" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B56,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B56,Узлы!$A$2:$A$85,0))</f>
         <v>м²</v>
       </c>
       <c r="E56" s="8">
@@ -2425,11 +2425,11 @@
         <v>6.0</v>
       </c>
       <c r="F56" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B56,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B56,Узлы!$A$2:$A$85,0))</f>
         <v>80.0</v>
       </c>
       <c r="G56" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B56,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B56,Узлы!$A$2:$A$85,0))</f>
         <v>140.0</v>
       </c>
       <c r="H56" s="9">
@@ -2460,11 +2460,11 @@
         </is>
       </c>
       <c r="C57" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B57,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B57,Узлы!$A$2:$A$85,0))</f>
         <v>Молдинги на стенах</v>
       </c>
       <c r="D57" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B57,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B57,Узлы!$A$2:$A$85,0))</f>
         <v>м.п.</v>
       </c>
       <c r="E57" s="8">
@@ -2472,11 +2472,11 @@
         <v>15.0</v>
       </c>
       <c r="F57" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B57,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B57,Узлы!$A$2:$A$85,0))</f>
         <v>15.0</v>
       </c>
       <c r="G57" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B57,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B57,Узлы!$A$2:$A$85,0))</f>
         <v>12.0</v>
       </c>
       <c r="H57" s="9">
@@ -2507,22 +2507,22 @@
         </is>
       </c>
       <c r="C58" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B58,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B58,Узлы!$A$2:$A$85,0))</f>
         <v>Микроцемент стены санузла (МКЦ-1) — фикс студии до 20 м², €1 120</v>
       </c>
       <c r="D58" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B58,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B58,Узлы!$A$2:$A$85,0))</f>
         <v>объект</v>
       </c>
       <c r="E58" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F58" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B58,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B58,Узлы!$A$2:$A$85,0))</f>
         <v>1689.863</v>
       </c>
       <c r="G58" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B58,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B58,Узлы!$A$2:$A$85,0))</f>
         <v>2172.681</v>
       </c>
       <c r="H58" s="9">
@@ -2553,22 +2553,22 @@
         </is>
       </c>
       <c r="C59" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B59,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B59,Узлы!$A$2:$A$85,0))</f>
         <v>Расходники микроцемент на объект</v>
       </c>
       <c r="D59" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B59,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B59,Узлы!$A$2:$A$85,0))</f>
         <v>объект</v>
       </c>
       <c r="E59" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F59" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B59,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B59,Узлы!$A$2:$A$85,0))</f>
         <v>0.0</v>
       </c>
       <c r="G59" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B59,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B59,Узлы!$A$2:$A$85,0))</f>
         <v>275.896</v>
       </c>
       <c r="H59" s="9">
@@ -2635,11 +2635,11 @@
         </is>
       </c>
       <c r="C63" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B63,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B63,Узлы!$A$2:$A$85,0))</f>
         <v>Электроточка полная: розетка/выключатель/вывод (штроба + кабель + подрозетник + механизм)</v>
       </c>
       <c r="D63" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B63,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B63,Узлы!$A$2:$A$85,0))</f>
         <v>точка</v>
       </c>
       <c r="E63" s="8">
@@ -2647,11 +2647,11 @@
         <v>101.0</v>
       </c>
       <c r="F63" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B63,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B63,Узлы!$A$2:$A$85,0))</f>
         <v>90.0</v>
       </c>
       <c r="G63" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B63,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B63,Узлы!$A$2:$A$85,0))</f>
         <v>42.0</v>
       </c>
       <c r="H63" s="9">
@@ -2682,11 +2682,11 @@
         </is>
       </c>
       <c r="C64" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B64,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B64,Узлы!$A$2:$A$85,0))</f>
         <v>Точка света (вывод + подключение светильника)</v>
       </c>
       <c r="D64" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B64,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B64,Узлы!$A$2:$A$85,0))</f>
         <v>шт</v>
       </c>
       <c r="E64" s="8">
@@ -2694,11 +2694,11 @@
         <v>55.0</v>
       </c>
       <c r="F64" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B64,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B64,Узлы!$A$2:$A$85,0))</f>
         <v>35.0</v>
       </c>
       <c r="G64" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B64,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B64,Узлы!$A$2:$A$85,0))</f>
         <v>16.0</v>
       </c>
       <c r="H64" s="9">
@@ -2729,22 +2729,22 @@
         </is>
       </c>
       <c r="C65" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B65,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B65,Узлы!$A$2:$A$85,0))</f>
         <v>Шинопровод Flexy TREK 3 м + 4 светильника</v>
       </c>
       <c r="D65" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B65,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B65,Узлы!$A$2:$A$85,0))</f>
         <v>компл</v>
       </c>
       <c r="E65" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F65" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B65,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B65,Узлы!$A$2:$A$85,0))</f>
         <v>360.0</v>
       </c>
       <c r="G65" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B65,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B65,Узлы!$A$2:$A$85,0))</f>
         <v>0.0</v>
       </c>
       <c r="H65" s="9">
@@ -2775,22 +2775,22 @@
         </is>
       </c>
       <c r="C66" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B66,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B66,Узлы!$A$2:$A$85,0))</f>
         <v>LED-подсветка в профилях Laconistiq, карнизах, мебели (монтаж ленты и БП)</v>
       </c>
       <c r="D66" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B66,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B66,Узлы!$A$2:$A$85,0))</f>
         <v>м.п.</v>
       </c>
       <c r="E66" s="11" t="n">
         <v>20</v>
       </c>
       <c r="F66" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B66,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B66,Узлы!$A$2:$A$85,0))</f>
         <v>27.0</v>
       </c>
       <c r="G66" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B66,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B66,Узлы!$A$2:$A$85,0))</f>
         <v>25.0</v>
       </c>
       <c r="H66" s="9">
@@ -2821,22 +2821,22 @@
         </is>
       </c>
       <c r="C67" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B67,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B67,Узлы!$A$2:$A$85,0))</f>
         <v>Щит квартирный 24–36 модулей, сборка</v>
       </c>
       <c r="D67" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B67,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B67,Узлы!$A$2:$A$85,0))</f>
         <v>шт</v>
       </c>
       <c r="E67" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F67" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B67,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B67,Узлы!$A$2:$A$85,0))</f>
         <v>900.0</v>
       </c>
       <c r="G67" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B67,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B67,Узлы!$A$2:$A$85,0))</f>
         <v>800.0</v>
       </c>
       <c r="H67" s="9">
@@ -2863,22 +2863,22 @@
         </is>
       </c>
       <c r="C68" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B68,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B68,Узлы!$A$2:$A$85,0))</f>
         <v>Слаботочка: интернет-кабель к 4 розеткам RJ45</v>
       </c>
       <c r="D68" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B68,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B68,Узлы!$A$2:$A$85,0))</f>
         <v>м.п.</v>
       </c>
       <c r="E68" s="11" t="n">
         <v>40</v>
       </c>
       <c r="F68" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B68,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B68,Узлы!$A$2:$A$85,0))</f>
         <v>4.0</v>
       </c>
       <c r="G68" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B68,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B68,Узлы!$A$2:$A$85,0))</f>
         <v>1.5</v>
       </c>
       <c r="H68" s="9">
@@ -2945,11 +2945,11 @@
         </is>
       </c>
       <c r="C72" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B72,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B72,Узлы!$A$2:$A$85,0))</f>
         <v>Точка водоснабжения (ХВС/ГВС, PPR/PEX)</v>
       </c>
       <c r="D72" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B72,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B72,Узлы!$A$2:$A$85,0))</f>
         <v>точка</v>
       </c>
       <c r="E72" s="8">
@@ -2957,11 +2957,11 @@
         <v>9.0</v>
       </c>
       <c r="F72" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B72,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B72,Узлы!$A$2:$A$85,0))</f>
         <v>70.0</v>
       </c>
       <c r="G72" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B72,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B72,Узлы!$A$2:$A$85,0))</f>
         <v>22.0</v>
       </c>
       <c r="H72" s="9">
@@ -2992,11 +2992,11 @@
         </is>
       </c>
       <c r="C73" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B73,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B73,Узлы!$A$2:$A$85,0))</f>
         <v>Точка канализации</v>
       </c>
       <c r="D73" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B73,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B73,Узлы!$A$2:$A$85,0))</f>
         <v>точка</v>
       </c>
       <c r="E73" s="8">
@@ -3004,11 +3004,11 @@
         <v>5.0</v>
       </c>
       <c r="F73" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B73,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B73,Узлы!$A$2:$A$85,0))</f>
         <v>45.0</v>
       </c>
       <c r="G73" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B73,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B73,Узлы!$A$2:$A$85,0))</f>
         <v>14.0</v>
       </c>
       <c r="H73" s="9">
@@ -3039,22 +3039,22 @@
         </is>
       </c>
       <c r="C74" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B74,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B74,Узлы!$A$2:$A$85,0))</f>
         <v>Узел ввода: краны, фильтры, редукторы, счётчики, коллекторы (2 стояка)</v>
       </c>
       <c r="D74" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B74,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B74,Узлы!$A$2:$A$85,0))</f>
         <v>компл</v>
       </c>
       <c r="E74" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F74" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B74,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B74,Узлы!$A$2:$A$85,0))</f>
         <v>300.0</v>
       </c>
       <c r="G74" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B74,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B74,Узлы!$A$2:$A$85,0))</f>
         <v>770.0</v>
       </c>
       <c r="H74" s="9">
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="C75" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B75,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B75,Узлы!$A$2:$A$85,0))</f>
         <v>Инсталляция TECE + навеска унитаза Roca The Gap</v>
       </c>
       <c r="D75" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B75,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B75,Узлы!$A$2:$A$85,0))</f>
         <v>компл</v>
       </c>
       <c r="E75" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F75" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B75,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B75,Узлы!$A$2:$A$85,0))</f>
         <v>285.0</v>
       </c>
       <c r="G75" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B75,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B75,Узлы!$A$2:$A$85,0))</f>
         <v>0.0</v>
       </c>
       <c r="H75" s="9">
@@ -3131,22 +3131,22 @@
         </is>
       </c>
       <c r="C76" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B76,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B76,Узлы!$A$2:$A$85,0))</f>
         <v>Ванна Kaldewei Eurowa 170×70 с ножками и шумоизоляцией, установка</v>
       </c>
       <c r="D76" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B76,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B76,Узлы!$A$2:$A$85,0))</f>
         <v>шт</v>
       </c>
       <c r="E76" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F76" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B76,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B76,Узлы!$A$2:$A$85,0))</f>
         <v>130.0</v>
       </c>
       <c r="G76" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B76,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B76,Узлы!$A$2:$A$85,0))</f>
         <v>20.0</v>
       </c>
       <c r="H76" s="9">
@@ -3177,22 +3177,22 @@
         </is>
       </c>
       <c r="C77" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B77,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B77,Узлы!$A$2:$A$85,0))</f>
         <v>Скрытый смеситель (раковина, гиг. душ) — встроенная + лицевая часть</v>
       </c>
       <c r="D77" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B77,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B77,Узлы!$A$2:$A$85,0))</f>
         <v>шт</v>
       </c>
       <c r="E77" s="11" t="n">
         <v>2</v>
       </c>
       <c r="F77" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B77,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B77,Узлы!$A$2:$A$85,0))</f>
         <v>380.0</v>
       </c>
       <c r="G77" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B77,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B77,Узлы!$A$2:$A$85,0))</f>
         <v>0.0</v>
       </c>
       <c r="H77" s="9">
@@ -3223,22 +3223,22 @@
         </is>
       </c>
       <c r="C78" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B78,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B78,Узлы!$A$2:$A$85,0))</f>
         <v>Душевая система MOZA со скрытым сливом: смеситель + трап/лоток</v>
       </c>
       <c r="D78" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B78,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B78,Узлы!$A$2:$A$85,0))</f>
         <v>компл</v>
       </c>
       <c r="E78" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F78" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B78,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B78,Узлы!$A$2:$A$85,0))</f>
         <v>500.0</v>
       </c>
       <c r="G78" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B78,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B78,Узлы!$A$2:$A$85,0))</f>
         <v>0.0</v>
       </c>
       <c r="H78" s="9">
@@ -3269,22 +3269,22 @@
         </is>
       </c>
       <c r="C79" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B79,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B79,Узлы!$A$2:$A$85,0))</f>
         <v>Смеситель кухонный, умывальник, подключение СМ/ПМ, водонагреватель проточный</v>
       </c>
       <c r="D79" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B79,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B79,Узлы!$A$2:$A$85,0))</f>
         <v>компл</v>
       </c>
       <c r="E79" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F79" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B79,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B79,Узлы!$A$2:$A$85,0))</f>
         <v>410.0</v>
       </c>
       <c r="G79" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B79,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B79,Узлы!$A$2:$A$85,0))</f>
         <v>30.0</v>
       </c>
       <c r="H79" s="9">
@@ -3315,22 +3315,22 @@
         </is>
       </c>
       <c r="C80" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B80,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B80,Узлы!$A$2:$A$85,0))</f>
         <v>Полотенцесушитель электрический Сунержа Богема, навеска</v>
       </c>
       <c r="D80" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B80,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B80,Узлы!$A$2:$A$85,0))</f>
         <v>шт</v>
       </c>
       <c r="E80" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F80" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B80,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B80,Узлы!$A$2:$A$85,0))</f>
         <v>120.0</v>
       </c>
       <c r="G80" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B80,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B80,Узлы!$A$2:$A$85,0))</f>
         <v>5.0</v>
       </c>
       <c r="H80" s="9">
@@ -3361,22 +3361,22 @@
         </is>
       </c>
       <c r="C81" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B81,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B81,Узлы!$A$2:$A$85,0))</f>
         <v>Радиатор Royal Thermo Insignia, замена с подводом</v>
       </c>
       <c r="D81" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B81,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B81,Узлы!$A$2:$A$85,0))</f>
         <v>шт</v>
       </c>
       <c r="E81" s="11" t="n">
         <v>2</v>
       </c>
       <c r="F81" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B81,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B81,Узлы!$A$2:$A$85,0))</f>
         <v>150.0</v>
       </c>
       <c r="G81" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B81,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B81,Узлы!$A$2:$A$85,0))</f>
         <v>40.0</v>
       </c>
       <c r="H81" s="9">
@@ -3407,22 +3407,22 @@
         </is>
       </c>
       <c r="C82" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B82,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B82,Узлы!$A$2:$A$85,0))</f>
         <v>Шумоизоляция стояков и термоизоляция труб ХВС/ГВС</v>
       </c>
       <c r="D82" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B82,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B82,Узлы!$A$2:$A$85,0))</f>
         <v>компл</v>
       </c>
       <c r="E82" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F82" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B82,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B82,Узлы!$A$2:$A$85,0))</f>
         <v>160.0</v>
       </c>
       <c r="G82" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B82,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B82,Узлы!$A$2:$A$85,0))</f>
         <v>60.0</v>
       </c>
       <c r="H82" s="9">
@@ -3467,7 +3467,7 @@
       <c r="B85" s="4" t="n"/>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>9. Двери и завершение</t>
+          <t>9. Вентиляция и прочие скрытые работы</t>
         </is>
       </c>
       <c r="D85" s="4" t="n"/>
@@ -3485,44 +3485,43 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>M56</t>
+          <t>V01</t>
         </is>
       </c>
       <c r="C86" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B86,Узлы!$A$2:$A$59,0))</f>
-        <v>Установка межкомнатных дверей (ДВ-1 700 ×1, ДВ-2 800 ×2)</v>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B86,Узлы!$A$2:$A$85,0))</f>
+        <v>Кухня: приточно-вытяжная решётка с клапаном в существующий вентканал</v>
       </c>
       <c r="D86" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B86,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B86,Узлы!$A$2:$A$85,0))</f>
         <v>шт</v>
       </c>
-      <c r="E86" s="8">
-        <f>Объёмы!$B$40</f>
-        <v>3.0</v>
+      <c r="E86" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="F86" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B86,Узлы!$A$2:$A$59,0))</f>
-        <v>118.0</v>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B86,Узлы!$A$2:$A$85,0))</f>
+        <v>30.0</v>
       </c>
       <c r="G86" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B86,Узлы!$A$2:$A$59,0))</f>
-        <v>15.0</v>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B86,Узлы!$A$2:$A$85,0))</f>
+        <v>25.0</v>
       </c>
       <c r="H86" s="9">
         <f>E86*F86</f>
-        <v>354.0</v>
+        <v>30.0</v>
       </c>
       <c r="I86" s="9">
         <f>E86*G86</f>
-        <v>45.0</v>
+        <v>25.0</v>
       </c>
       <c r="J86" s="9">
         <f>H86+I86</f>
-        <v>399.0</v>
+        <v>55.0</v>
       </c>
       <c r="K86" s="10" t="inlineStr">
         <is>
-          <t>лист 21</t>
+          <t>кухня, естественная вытяжка</t>
         </is>
       </c>
     </row>
@@ -3532,43 +3531,43 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>M57</t>
+          <t>V02</t>
         </is>
       </c>
       <c r="C87" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B87,Узлы!$A$2:$A$59,0))</f>
-        <v>Установка входной двери</v>
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B87,Узлы!$A$2:$A$85,0))</f>
+        <v>Кухонная вытяжка: воздуховод ПВХ 125 (≈3 м) с обратным клапаном к вентканалу, скрыто за кухней</v>
       </c>
       <c r="D87" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B87,Узлы!$A$2:$A$59,0))</f>
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B87,Узлы!$A$2:$A$85,0))</f>
         <v>шт</v>
       </c>
       <c r="E87" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F87" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B87,Узлы!$A$2:$A$59,0))</f>
-        <v>110.0</v>
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B87,Узлы!$A$2:$A$85,0))</f>
+        <v>120.0</v>
       </c>
       <c r="G87" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B87,Узлы!$A$2:$A$59,0))</f>
-        <v>25.0</v>
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B87,Узлы!$A$2:$A$85,0))</f>
+        <v>80.0</v>
       </c>
       <c r="H87" s="9">
         <f>E87*F87</f>
-        <v>110.0</v>
+        <v>120.0</v>
       </c>
       <c r="I87" s="9">
         <f>E87*G87</f>
-        <v>25.0</v>
+        <v>80.0</v>
       </c>
       <c r="J87" s="9">
         <f>H87+I87</f>
-        <v>135.0</v>
+        <v>200.0</v>
       </c>
       <c r="K87" s="10" t="inlineStr">
         <is>
-          <t>лист 26</t>
+          <t>кухонная вытяжка в канал</t>
         </is>
       </c>
     </row>
@@ -3578,301 +3577,1632 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
+          <t>V03</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="str">
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B88,Узлы!$A$2:$A$85,0))</f>
+        <v>Зона стиральной машины: накладной/канальный вентилятор 100 мм с обратным клапаном и воздуховодом</v>
+      </c>
+      <c r="D88" s="7" t="str">
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B88,Узлы!$A$2:$A$85,0))</f>
+        <v>шт</v>
+      </c>
+      <c r="E88" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" s="8">
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B88,Узлы!$A$2:$A$85,0))</f>
+        <v>90.0</v>
+      </c>
+      <c r="G88" s="8">
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B88,Узлы!$A$2:$A$85,0))</f>
+        <v>105.0</v>
+      </c>
+      <c r="H88" s="9">
+        <f>E88*F88</f>
+        <v>90.0</v>
+      </c>
+      <c r="I88" s="9">
+        <f>E88*G88</f>
+        <v>105.0</v>
+      </c>
+      <c r="J88" s="9">
+        <f>H88+I88</f>
+        <v>195.0</v>
+      </c>
+      <c r="K88" s="10" t="inlineStr">
+        <is>
+          <t>зона стиральной машины</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>V04</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="str">
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B89,Узлы!$A$2:$A$85,0))</f>
+        <v>Санузел: вентилятор 100 мм с таймером и обратным клапаном под скрытую решётку</v>
+      </c>
+      <c r="D89" s="7" t="str">
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B89,Узлы!$A$2:$A$85,0))</f>
+        <v>шт</v>
+      </c>
+      <c r="E89" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" s="8">
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B89,Узлы!$A$2:$A$85,0))</f>
+        <v>60.0</v>
+      </c>
+      <c r="G89" s="8">
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B89,Узлы!$A$2:$A$85,0))</f>
+        <v>110.0</v>
+      </c>
+      <c r="H89" s="9">
+        <f>E89*F89</f>
+        <v>60.0</v>
+      </c>
+      <c r="I89" s="9">
+        <f>E89*G89</f>
+        <v>110.0</v>
+      </c>
+      <c r="J89" s="9">
+        <f>H89+I89</f>
+        <v>170.0</v>
+      </c>
+      <c r="K89" s="10" t="inlineStr">
+        <is>
+          <t>санузел, под скрытую решётку</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>H01</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="str">
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B90,Узлы!$A$2:$A$85,0))</f>
+        <v>Закладные под подвесную мебель, тумбу умывальника, зеркала, полки (фанера/брус в перегородках)</v>
+      </c>
+      <c r="D90" s="7" t="str">
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B90,Узлы!$A$2:$A$85,0))</f>
+        <v>компл</v>
+      </c>
+      <c r="E90" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" s="8">
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B90,Узлы!$A$2:$A$85,0))</f>
+        <v>150.0</v>
+      </c>
+      <c r="G90" s="8">
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B90,Узлы!$A$2:$A$85,0))</f>
+        <v>60.0</v>
+      </c>
+      <c r="H90" s="9">
+        <f>E90*F90</f>
+        <v>150.0</v>
+      </c>
+      <c r="I90" s="9">
+        <f>E90*G90</f>
+        <v>60.0</v>
+      </c>
+      <c r="J90" s="9">
+        <f>H90+I90</f>
+        <v>210.0</v>
+      </c>
+      <c r="K90" s="10" t="inlineStr">
+        <is>
+          <t>лист 4 п. 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>H02</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="str">
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B91,Узлы!$A$2:$A$85,0))</f>
+        <v>Заделка отверстий и штроб после демонтажа радиаторов, щитка, старых выводов</v>
+      </c>
+      <c r="D91" s="7" t="str">
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B91,Узлы!$A$2:$A$85,0))</f>
+        <v>компл</v>
+      </c>
+      <c r="E91" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" s="8">
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B91,Узлы!$A$2:$A$85,0))</f>
+        <v>100.0</v>
+      </c>
+      <c r="G91" s="8">
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B91,Узлы!$A$2:$A$85,0))</f>
+        <v>30.0</v>
+      </c>
+      <c r="H91" s="9">
+        <f>E91*F91</f>
+        <v>100.0</v>
+      </c>
+      <c r="I91" s="9">
+        <f>E91*G91</f>
+        <v>30.0</v>
+      </c>
+      <c r="J91" s="9">
+        <f>H91+I91</f>
+        <v>130.0</v>
+      </c>
+      <c r="K91" s="10" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="C92" s="12" t="inlineStr">
+        <is>
+          <t>Итого по разделу</t>
+        </is>
+      </c>
+      <c r="H92" s="13">
+        <f>SUM(H86:H91)</f>
+        <v>550.0</v>
+      </c>
+      <c r="I92" s="13">
+        <f>SUM(I86:I91)</f>
+        <v>410.0</v>
+      </c>
+      <c r="J92" s="13">
+        <f>SUM(J86:J91)</f>
+        <v>960.0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="n"/>
+      <c r="B94" s="4" t="n"/>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>10. Балкон: утепление и основание</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="n"/>
+      <c r="E94" s="4" t="n"/>
+      <c r="F94" s="4" t="n"/>
+      <c r="G94" s="4" t="n"/>
+      <c r="H94" s="4" t="n"/>
+      <c r="I94" s="4" t="n"/>
+      <c r="J94" s="4" t="n"/>
+      <c r="K94" s="4" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>B01</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="str">
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B95,Узлы!$A$2:$A$85,0))</f>
+        <v>Утепление парапета и боковых стен балкона ЭППС 50 мм на клей-пену с дюбелями, швы пеной</v>
+      </c>
+      <c r="D95" s="7" t="str">
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B95,Узлы!$A$2:$A$85,0))</f>
+        <v>м²</v>
+      </c>
+      <c r="E95" s="8">
+        <f>Объёмы!$B$41</f>
+        <v>10.324</v>
+      </c>
+      <c r="F95" s="8">
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B95,Узлы!$A$2:$A$85,0))</f>
+        <v>25.0</v>
+      </c>
+      <c r="G95" s="8">
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B95,Узлы!$A$2:$A$85,0))</f>
+        <v>16.0</v>
+      </c>
+      <c r="H95" s="9">
+        <f>E95*F95</f>
+        <v>258.1</v>
+      </c>
+      <c r="I95" s="9">
+        <f>E95*G95</f>
+        <v>165.184</v>
+      </c>
+      <c r="J95" s="9">
+        <f>H95+I95</f>
+        <v>423.284</v>
+      </c>
+      <c r="K95" s="10" t="inlineStr">
+        <is>
+          <t>остекление существующее; замена на тёплое не включена</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>B02</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="str">
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B96,Узлы!$A$2:$A$85,0))</f>
+        <v>Пароизоляция фольгированная (пенофол 5 мм) с проклейкой швов, стены и потолок балкона</v>
+      </c>
+      <c r="D96" s="7" t="str">
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B96,Узлы!$A$2:$A$85,0))</f>
+        <v>м²</v>
+      </c>
+      <c r="E96" s="8">
+        <f>Объёмы!$B$44</f>
+        <v>13.474</v>
+      </c>
+      <c r="F96" s="8">
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B96,Узлы!$A$2:$A$85,0))</f>
+        <v>5.0</v>
+      </c>
+      <c r="G96" s="8">
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B96,Узлы!$A$2:$A$85,0))</f>
+        <v>7.0</v>
+      </c>
+      <c r="H96" s="9">
+        <f>E96*F96</f>
+        <v>67.37</v>
+      </c>
+      <c r="I96" s="9">
+        <f>E96*G96</f>
+        <v>94.318</v>
+      </c>
+      <c r="J96" s="9">
+        <f>H96+I96</f>
+        <v>161.688</v>
+      </c>
+      <c r="K96" s="10" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>B03</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="str">
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B97,Узлы!$A$2:$A$85,0))</f>
+        <v>Каркас и обшивка ГКЛВ парапета и боковых стен балкона (под обои ОБ-1)</v>
+      </c>
+      <c r="D97" s="7" t="str">
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B97,Узлы!$A$2:$A$85,0))</f>
+        <v>м²</v>
+      </c>
+      <c r="E97" s="8">
+        <f>Объёмы!$B$41</f>
+        <v>10.324</v>
+      </c>
+      <c r="F97" s="8">
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B97,Узлы!$A$2:$A$85,0))</f>
+        <v>45.0</v>
+      </c>
+      <c r="G97" s="8">
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B97,Узлы!$A$2:$A$85,0))</f>
+        <v>15.0</v>
+      </c>
+      <c r="H97" s="9">
+        <f>E97*F97</f>
+        <v>464.58</v>
+      </c>
+      <c r="I97" s="9">
+        <f>E97*G97</f>
+        <v>154.86</v>
+      </c>
+      <c r="J97" s="9">
+        <f>H97+I97</f>
+        <v>619.44</v>
+      </c>
+      <c r="K97" s="10" t="inlineStr">
+        <is>
+          <t>под обои ОБ-1 (шпаклёвка учтена в разделе 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>B04</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="str">
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B98,Узлы!$A$2:$A$85,0))</f>
+        <v>Утепление потолка балкона ЭППС 50 мм + пароизоляция (под натяжной потолок)</v>
+      </c>
+      <c r="D98" s="7" t="str">
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B98,Узлы!$A$2:$A$85,0))</f>
+        <v>м²</v>
+      </c>
+      <c r="E98" s="8">
+        <f>Объёмы!$B$42</f>
+        <v>3.15</v>
+      </c>
+      <c r="F98" s="8">
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B98,Узлы!$A$2:$A$85,0))</f>
+        <v>30.0</v>
+      </c>
+      <c r="G98" s="8">
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B98,Узлы!$A$2:$A$85,0))</f>
+        <v>23.0</v>
+      </c>
+      <c r="H98" s="9">
+        <f>E98*F98</f>
+        <v>94.5</v>
+      </c>
+      <c r="I98" s="9">
+        <f>E98*G98</f>
+        <v>72.45</v>
+      </c>
+      <c r="J98" s="9">
+        <f>H98+I98</f>
+        <v>166.95</v>
+      </c>
+      <c r="K98" s="10" t="inlineStr">
+        <is>
+          <t>натяжной потолок учтён в разделе 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>B05</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="str">
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B99,Узлы!$A$2:$A$85,0))</f>
+        <v>Пол балкона: ЭППС 50 мм, плёнка, стяжка ЦПС 50 мм с сеткой до уровня квартиры</v>
+      </c>
+      <c r="D99" s="7" t="str">
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B99,Узлы!$A$2:$A$85,0))</f>
+        <v>м²</v>
+      </c>
+      <c r="E99" s="8">
+        <f>Объёмы!$B$43</f>
+        <v>3.15</v>
+      </c>
+      <c r="F99" s="8">
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B99,Узлы!$A$2:$A$85,0))</f>
+        <v>40.0</v>
+      </c>
+      <c r="G99" s="8">
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B99,Узлы!$A$2:$A$85,0))</f>
+        <v>51.0</v>
+      </c>
+      <c r="H99" s="9">
+        <f>E99*F99</f>
+        <v>126.0</v>
+      </c>
+      <c r="I99" s="9">
+        <f>E99*G99</f>
+        <v>160.65</v>
+      </c>
+      <c r="J99" s="9">
+        <f>H99+I99</f>
+        <v>286.65</v>
+      </c>
+      <c r="K99" s="10" t="inlineStr">
+        <is>
+          <t>винил на балконе учтён в 49 м² раздела 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>B06</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="str">
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B100,Узлы!$A$2:$A$85,0))</f>
+        <v>Герметизация примыканий остекления и балконного блока: пена, герметик, откосы</v>
+      </c>
+      <c r="D100" s="7" t="str">
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B100,Узлы!$A$2:$A$85,0))</f>
+        <v>м.п.</v>
+      </c>
+      <c r="E100" s="8">
+        <f>Объёмы!$B$45</f>
+        <v>9.56</v>
+      </c>
+      <c r="F100" s="8">
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B100,Узлы!$A$2:$A$85,0))</f>
+        <v>10.0</v>
+      </c>
+      <c r="G100" s="8">
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B100,Узлы!$A$2:$A$85,0))</f>
+        <v>5.0</v>
+      </c>
+      <c r="H100" s="9">
+        <f>E100*F100</f>
+        <v>95.6</v>
+      </c>
+      <c r="I100" s="9">
+        <f>E100*G100</f>
+        <v>47.8</v>
+      </c>
+      <c r="J100" s="9">
+        <f>H100+I100</f>
+        <v>143.4</v>
+      </c>
+      <c r="K100" s="10" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="C101" s="12" t="inlineStr">
+        <is>
+          <t>Итого по разделу</t>
+        </is>
+      </c>
+      <c r="H101" s="13">
+        <f>SUM(H95:H100)</f>
+        <v>1106.15</v>
+      </c>
+      <c r="I101" s="13">
+        <f>SUM(I95:I100)</f>
+        <v>695.262</v>
+      </c>
+      <c r="J101" s="13">
+        <f>SUM(J95:J100)</f>
+        <v>1801.412</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="n"/>
+      <c r="B103" s="4" t="n"/>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>11. Двери и завершение</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="n"/>
+      <c r="E103" s="4" t="n"/>
+      <c r="F103" s="4" t="n"/>
+      <c r="G103" s="4" t="n"/>
+      <c r="H103" s="4" t="n"/>
+      <c r="I103" s="4" t="n"/>
+      <c r="J103" s="4" t="n"/>
+      <c r="K103" s="4" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>M56</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="str">
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B104,Узлы!$A$2:$A$85,0))</f>
+        <v>Установка межкомнатных дверей (ДВ-1 700 ×1, ДВ-2 800 ×2)</v>
+      </c>
+      <c r="D104" s="7" t="str">
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B104,Узлы!$A$2:$A$85,0))</f>
+        <v>шт</v>
+      </c>
+      <c r="E104" s="8">
+        <f>Объёмы!$B$40</f>
+        <v>3.0</v>
+      </c>
+      <c r="F104" s="8">
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B104,Узлы!$A$2:$A$85,0))</f>
+        <v>118.0</v>
+      </c>
+      <c r="G104" s="8">
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B104,Узлы!$A$2:$A$85,0))</f>
+        <v>15.0</v>
+      </c>
+      <c r="H104" s="9">
+        <f>E104*F104</f>
+        <v>354.0</v>
+      </c>
+      <c r="I104" s="9">
+        <f>E104*G104</f>
+        <v>45.0</v>
+      </c>
+      <c r="J104" s="9">
+        <f>H104+I104</f>
+        <v>399.0</v>
+      </c>
+      <c r="K104" s="10" t="inlineStr">
+        <is>
+          <t>лист 21</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>M57</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="str">
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B105,Узлы!$A$2:$A$85,0))</f>
+        <v>Установка входной двери</v>
+      </c>
+      <c r="D105" s="7" t="str">
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B105,Узлы!$A$2:$A$85,0))</f>
+        <v>шт</v>
+      </c>
+      <c r="E105" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" s="8">
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B105,Узлы!$A$2:$A$85,0))</f>
+        <v>110.0</v>
+      </c>
+      <c r="G105" s="8">
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B105,Узлы!$A$2:$A$85,0))</f>
+        <v>25.0</v>
+      </c>
+      <c r="H105" s="9">
+        <f>E105*F105</f>
+        <v>110.0</v>
+      </c>
+      <c r="I105" s="9">
+        <f>E105*G105</f>
+        <v>25.0</v>
+      </c>
+      <c r="J105" s="9">
+        <f>H105+I105</f>
+        <v>135.0</v>
+      </c>
+      <c r="K105" s="10" t="inlineStr">
+        <is>
+          <t>лист 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
           <t>M58</t>
         </is>
       </c>
-      <c r="C88" s="7" t="str">
-        <f>INDEX(Узлы!$B$2:$B$59,MATCH(B88,Узлы!$A$2:$A$59,0))</f>
+      <c r="C106" s="7" t="str">
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B106,Узлы!$A$2:$A$85,0))</f>
         <v>Уборка после ремонта</v>
       </c>
-      <c r="D88" s="7" t="str">
-        <f>INDEX(Узлы!$C$2:$C$59,MATCH(B88,Узлы!$A$2:$A$59,0))</f>
+      <c r="D106" s="7" t="str">
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B106,Узлы!$A$2:$A$85,0))</f>
         <v>м²</v>
       </c>
-      <c r="E88" s="8">
+      <c r="E106" s="8">
         <f>Объёмы!$B$10</f>
         <v>57.03</v>
       </c>
-      <c r="F88" s="8">
-        <f>INDEX(Узлы!$G$2:$G$59,MATCH(B88,Узлы!$A$2:$A$59,0))</f>
+      <c r="F106" s="8">
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B106,Узлы!$A$2:$A$85,0))</f>
         <v>4.5</v>
       </c>
-      <c r="G88" s="8">
-        <f>INDEX(Узлы!$E$2:$E$59,MATCH(B88,Узлы!$A$2:$A$59,0))</f>
+      <c r="G106" s="8">
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B106,Узлы!$A$2:$A$85,0))</f>
         <v>0.0</v>
       </c>
-      <c r="H88" s="9">
-        <f>E88*F88</f>
+      <c r="H106" s="9">
+        <f>E106*F106</f>
         <v>256.635</v>
       </c>
-      <c r="I88" s="9">
-        <f>E88*G88</f>
+      <c r="I106" s="9">
+        <f>E106*G106</f>
         <v>0.0</v>
       </c>
-      <c r="J88" s="9">
-        <f>H88+I88</f>
+      <c r="J106" s="9">
+        <f>H106+I106</f>
         <v>256.635</v>
       </c>
-      <c r="K88" s="10" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="C89" s="12" t="inlineStr">
+      <c r="K106" s="10" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="C107" s="12" t="inlineStr">
         <is>
           <t>Итого по разделу</t>
         </is>
       </c>
-      <c r="H89" s="13">
-        <f>SUM(H86:H88)</f>
+      <c r="H107" s="13">
+        <f>SUM(H104:H106)</f>
         <v>720.635</v>
       </c>
-      <c r="I89" s="13">
-        <f>SUM(I86:I88)</f>
+      <c r="I107" s="13">
+        <f>SUM(I104:I106)</f>
         <v>70.0</v>
       </c>
-      <c r="J89" s="13">
-        <f>SUM(J86:J88)</f>
+      <c r="J107" s="13">
+        <f>SUM(J104:J106)</f>
         <v>790.635</v>
       </c>
     </row>
-    <row r="92">
-      <c r="C92" s="12" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="4" t="n"/>
+      <c r="B109" s="4" t="n"/>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>12. Приборы и изделия по спецификации проекта (ориентировочно)</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="n"/>
+      <c r="E109" s="4" t="n"/>
+      <c r="F109" s="4" t="n"/>
+      <c r="G109" s="4" t="n"/>
+      <c r="H109" s="4" t="n"/>
+      <c r="I109" s="4" t="n"/>
+      <c r="J109" s="4" t="n"/>
+      <c r="K109" s="4" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="str">
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B110,Узлы!$A$2:$A$85,0))</f>
+        <v>Инсталляция TECE + унитаз Roca The Gap Clean Rim с крышкой SoftClose + клавиша</v>
+      </c>
+      <c r="D110" s="7" t="str">
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B110,Узлы!$A$2:$A$85,0))</f>
+        <v>компл</v>
+      </c>
+      <c r="E110" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F110" s="8">
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B110,Узлы!$A$2:$A$85,0))</f>
+        <v>0.0</v>
+      </c>
+      <c r="G110" s="8">
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B110,Узлы!$A$2:$A$85,0))</f>
+        <v>1700.0</v>
+      </c>
+      <c r="H110" s="9">
+        <f>E110*F110</f>
+        <v>0.0</v>
+      </c>
+      <c r="I110" s="9">
+        <f>E110*G110</f>
+        <v>1700.0</v>
+      </c>
+      <c r="J110" s="9">
+        <f>H110+I110</f>
+        <v>1700.0</v>
+      </c>
+      <c r="K110" s="10" t="inlineStr">
+        <is>
+          <t>лист 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="str">
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B111,Узлы!$A$2:$A$85,0))</f>
+        <v>Ванна стальная Kaldewei Eurowa 170×70 с ножками и шумоизоляцией</v>
+      </c>
+      <c r="D111" s="7" t="str">
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B111,Узлы!$A$2:$A$85,0))</f>
+        <v>шт</v>
+      </c>
+      <c r="E111" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" s="8">
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B111,Узлы!$A$2:$A$85,0))</f>
+        <v>0.0</v>
+      </c>
+      <c r="G111" s="8">
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B111,Узлы!$A$2:$A$85,0))</f>
+        <v>900.0</v>
+      </c>
+      <c r="H111" s="9">
+        <f>E111*F111</f>
+        <v>0.0</v>
+      </c>
+      <c r="I111" s="9">
+        <f>E111*G111</f>
+        <v>900.0</v>
+      </c>
+      <c r="J111" s="9">
+        <f>H111+I111</f>
+        <v>900.0</v>
+      </c>
+      <c r="K111" s="10" t="inlineStr">
+        <is>
+          <t>лист 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="n">
+        <v>73</v>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="str">
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B112,Узлы!$A$2:$A$85,0))</f>
+        <v>Полотенцесушитель Сунержа Богема 3.1 800×500 электрический (МЭМ)</v>
+      </c>
+      <c r="D112" s="7" t="str">
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B112,Узлы!$A$2:$A$85,0))</f>
+        <v>шт</v>
+      </c>
+      <c r="E112" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F112" s="8">
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B112,Узлы!$A$2:$A$85,0))</f>
+        <v>0.0</v>
+      </c>
+      <c r="G112" s="8">
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B112,Узлы!$A$2:$A$85,0))</f>
+        <v>1100.0</v>
+      </c>
+      <c r="H112" s="9">
+        <f>E112*F112</f>
+        <v>0.0</v>
+      </c>
+      <c r="I112" s="9">
+        <f>E112*G112</f>
+        <v>1100.0</v>
+      </c>
+      <c r="J112" s="9">
+        <f>H112+I112</f>
+        <v>1100.0</v>
+      </c>
+      <c r="K112" s="10" t="inlineStr">
+        <is>
+          <t>лист 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="str">
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B113,Узлы!$A$2:$A$85,0))</f>
+        <v>Умывальник литой под заказ</v>
+      </c>
+      <c r="D113" s="7" t="str">
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B113,Узлы!$A$2:$A$85,0))</f>
+        <v>шт</v>
+      </c>
+      <c r="E113" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" s="8">
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B113,Узлы!$A$2:$A$85,0))</f>
+        <v>0.0</v>
+      </c>
+      <c r="G113" s="8">
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B113,Узлы!$A$2:$A$85,0))</f>
+        <v>800.0</v>
+      </c>
+      <c r="H113" s="9">
+        <f>E113*F113</f>
+        <v>0.0</v>
+      </c>
+      <c r="I113" s="9">
+        <f>E113*G113</f>
+        <v>800.0</v>
+      </c>
+      <c r="J113" s="9">
+        <f>H113+I113</f>
+        <v>800.0</v>
+      </c>
+      <c r="K113" s="10" t="inlineStr">
+        <is>
+          <t>лист 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="str">
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B114,Узлы!$A$2:$A$85,0))</f>
+        <v>Скрытые смесители MOZA 316L: раковина и гигиенический душ (биде)</v>
+      </c>
+      <c r="D114" s="7" t="str">
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B114,Узлы!$A$2:$A$85,0))</f>
+        <v>шт</v>
+      </c>
+      <c r="E114" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F114" s="8">
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B114,Узлы!$A$2:$A$85,0))</f>
+        <v>0.0</v>
+      </c>
+      <c r="G114" s="8">
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B114,Узлы!$A$2:$A$85,0))</f>
+        <v>550.0</v>
+      </c>
+      <c r="H114" s="9">
+        <f>E114*F114</f>
+        <v>0.0</v>
+      </c>
+      <c r="I114" s="9">
+        <f>E114*G114</f>
+        <v>1100.0</v>
+      </c>
+      <c r="J114" s="9">
+        <f>H114+I114</f>
+        <v>1100.0</v>
+      </c>
+      <c r="K114" s="10" t="inlineStr">
+        <is>
+          <t>лист 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="C115" s="7" t="str">
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B115,Узлы!$A$2:$A$85,0))</f>
+        <v>Душевая система MOZA 316L со скрытым сливом, смеситель на 3 отверстия, 2 режима</v>
+      </c>
+      <c r="D115" s="7" t="str">
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B115,Узлы!$A$2:$A$85,0))</f>
+        <v>компл</v>
+      </c>
+      <c r="E115" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F115" s="8">
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B115,Узлы!$A$2:$A$85,0))</f>
+        <v>0.0</v>
+      </c>
+      <c r="G115" s="8">
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B115,Узлы!$A$2:$A$85,0))</f>
+        <v>1800.0</v>
+      </c>
+      <c r="H115" s="9">
+        <f>E115*F115</f>
+        <v>0.0</v>
+      </c>
+      <c r="I115" s="9">
+        <f>E115*G115</f>
+        <v>1800.0</v>
+      </c>
+      <c r="J115" s="9">
+        <f>H115+I115</f>
+        <v>1800.0</v>
+      </c>
+      <c r="K115" s="10" t="inlineStr">
+        <is>
+          <t>лист 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="C116" s="7" t="str">
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B116,Узлы!$A$2:$A$85,0))</f>
+        <v>Смеситель кухонный Vieir V15019-L под фильтр + дозатор Paulmark</v>
+      </c>
+      <c r="D116" s="7" t="str">
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B116,Узлы!$A$2:$A$85,0))</f>
+        <v>компл</v>
+      </c>
+      <c r="E116" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F116" s="8">
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B116,Узлы!$A$2:$A$85,0))</f>
+        <v>0.0</v>
+      </c>
+      <c r="G116" s="8">
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B116,Узлы!$A$2:$A$85,0))</f>
+        <v>330.0</v>
+      </c>
+      <c r="H116" s="9">
+        <f>E116*F116</f>
+        <v>0.0</v>
+      </c>
+      <c r="I116" s="9">
+        <f>E116*G116</f>
+        <v>330.0</v>
+      </c>
+      <c r="J116" s="9">
+        <f>H116+I116</f>
+        <v>330.0</v>
+      </c>
+      <c r="K116" s="10" t="inlineStr">
+        <is>
+          <t>лист 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="str">
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B117,Узлы!$A$2:$A$85,0))</f>
+        <v>Проточный водонагреватель</v>
+      </c>
+      <c r="D117" s="7" t="str">
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B117,Узлы!$A$2:$A$85,0))</f>
+        <v>шт</v>
+      </c>
+      <c r="E117" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F117" s="8">
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B117,Узлы!$A$2:$A$85,0))</f>
+        <v>0.0</v>
+      </c>
+      <c r="G117" s="8">
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B117,Узлы!$A$2:$A$85,0))</f>
+        <v>350.0</v>
+      </c>
+      <c r="H117" s="9">
+        <f>E117*F117</f>
+        <v>0.0</v>
+      </c>
+      <c r="I117" s="9">
+        <f>E117*G117</f>
+        <v>350.0</v>
+      </c>
+      <c r="J117" s="9">
+        <f>H117+I117</f>
+        <v>350.0</v>
+      </c>
+      <c r="K117" s="10" t="inlineStr">
+        <is>
+          <t>лист 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>P09</t>
+        </is>
+      </c>
+      <c r="C118" s="7" t="str">
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B118,Узлы!$A$2:$A$85,0))</f>
+        <v>Зеркало с подсветкой (санузел) и зеркало (прихожая)</v>
+      </c>
+      <c r="D118" s="7" t="str">
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B118,Узлы!$A$2:$A$85,0))</f>
+        <v>компл</v>
+      </c>
+      <c r="E118" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F118" s="8">
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B118,Узлы!$A$2:$A$85,0))</f>
+        <v>0.0</v>
+      </c>
+      <c r="G118" s="8">
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B118,Узлы!$A$2:$A$85,0))</f>
+        <v>800.0</v>
+      </c>
+      <c r="H118" s="9">
+        <f>E118*F118</f>
+        <v>0.0</v>
+      </c>
+      <c r="I118" s="9">
+        <f>E118*G118</f>
+        <v>800.0</v>
+      </c>
+      <c r="J118" s="9">
+        <f>H118+I118</f>
+        <v>800.0</v>
+      </c>
+      <c r="K118" s="10" t="inlineStr">
+        <is>
+          <t>лист 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="C119" s="7" t="str">
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B119,Узлы!$A$2:$A$85,0))</f>
+        <v>Радиатор стальной трубчатый Royal Thermo Insignia VC2180, 8 секций, RAL 9016</v>
+      </c>
+      <c r="D119" s="7" t="str">
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B119,Узлы!$A$2:$A$85,0))</f>
+        <v>шт</v>
+      </c>
+      <c r="E119" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F119" s="8">
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B119,Узлы!$A$2:$A$85,0))</f>
+        <v>0.0</v>
+      </c>
+      <c r="G119" s="8">
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B119,Узлы!$A$2:$A$85,0))</f>
+        <v>1100.0</v>
+      </c>
+      <c r="H119" s="9">
+        <f>E119*F119</f>
+        <v>0.0</v>
+      </c>
+      <c r="I119" s="9">
+        <f>E119*G119</f>
+        <v>2200.0</v>
+      </c>
+      <c r="J119" s="9">
+        <f>H119+I119</f>
+        <v>2200.0</v>
+      </c>
+      <c r="K119" s="10" t="inlineStr">
+        <is>
+          <t>лист 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="str">
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B120,Узлы!$A$2:$A$85,0))</f>
+        <v>Двери межкомнатные с коробкой, наличниками и фурнитурой (homeporte.by)</v>
+      </c>
+      <c r="D120" s="7" t="str">
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B120,Узлы!$A$2:$A$85,0))</f>
+        <v>шт</v>
+      </c>
+      <c r="E120" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F120" s="8">
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B120,Узлы!$A$2:$A$85,0))</f>
+        <v>0.0</v>
+      </c>
+      <c r="G120" s="8">
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B120,Узлы!$A$2:$A$85,0))</f>
+        <v>750.0</v>
+      </c>
+      <c r="H120" s="9">
+        <f>E120*F120</f>
+        <v>0.0</v>
+      </c>
+      <c r="I120" s="9">
+        <f>E120*G120</f>
+        <v>2250.0</v>
+      </c>
+      <c r="J120" s="9">
+        <f>H120+I120</f>
+        <v>2250.0</v>
+      </c>
+      <c r="K120" s="10" t="inlineStr">
+        <is>
+          <t>лист 21</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="C121" s="7" t="str">
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B121,Узлы!$A$2:$A$85,0))</f>
+        <v>Входная дверь (joinery.by)</v>
+      </c>
+      <c r="D121" s="7" t="str">
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B121,Узлы!$A$2:$A$85,0))</f>
+        <v>шт</v>
+      </c>
+      <c r="E121" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F121" s="8">
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B121,Узлы!$A$2:$A$85,0))</f>
+        <v>0.0</v>
+      </c>
+      <c r="G121" s="8">
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B121,Узлы!$A$2:$A$85,0))</f>
+        <v>2000.0</v>
+      </c>
+      <c r="H121" s="9">
+        <f>E121*F121</f>
+        <v>0.0</v>
+      </c>
+      <c r="I121" s="9">
+        <f>E121*G121</f>
+        <v>2000.0</v>
+      </c>
+      <c r="J121" s="9">
+        <f>H121+I121</f>
+        <v>2000.0</v>
+      </c>
+      <c r="K121" s="10" t="inlineStr">
+        <is>
+          <t>лист 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="str">
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B122,Узлы!$A$2:$A$85,0))</f>
+        <v>Светильники по спецификации листа 10: 44 спота GU10, 5 подвесных, потолочный, трек Flexy 3 м + 4 светильника, скрытая решётка</v>
+      </c>
+      <c r="D122" s="7" t="str">
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B122,Узлы!$A$2:$A$85,0))</f>
+        <v>компл</v>
+      </c>
+      <c r="E122" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F122" s="8">
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B122,Узлы!$A$2:$A$85,0))</f>
+        <v>0.0</v>
+      </c>
+      <c r="G122" s="8">
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B122,Узлы!$A$2:$A$85,0))</f>
+        <v>4700.0</v>
+      </c>
+      <c r="H122" s="9">
+        <f>E122*F122</f>
+        <v>0.0</v>
+      </c>
+      <c r="I122" s="9">
+        <f>E122*G122</f>
+        <v>4700.0</v>
+      </c>
+      <c r="J122" s="9">
+        <f>H122+I122</f>
+        <v>4700.0</v>
+      </c>
+      <c r="K122" s="10" t="inlineStr">
+        <is>
+          <t>лист 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>P14</t>
+        </is>
+      </c>
+      <c r="C123" s="7" t="str">
+        <f>INDEX(Узлы!$B$2:$B$85,MATCH(B123,Узлы!$A$2:$A$85,0))</f>
+        <v>Розетки и выключатели серии Vertus сверх учтённых 12 руб./механизм</v>
+      </c>
+      <c r="D123" s="7" t="str">
+        <f>INDEX(Узлы!$C$2:$C$85,MATCH(B123,Узлы!$A$2:$A$85,0))</f>
+        <v>компл</v>
+      </c>
+      <c r="E123" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F123" s="8">
+        <f>INDEX(Узлы!$G$2:$G$85,MATCH(B123,Узлы!$A$2:$A$85,0))</f>
+        <v>0.0</v>
+      </c>
+      <c r="G123" s="8">
+        <f>INDEX(Узлы!$E$2:$E$85,MATCH(B123,Узлы!$A$2:$A$85,0))</f>
+        <v>1500.0</v>
+      </c>
+      <c r="H123" s="9">
+        <f>E123*F123</f>
+        <v>0.0</v>
+      </c>
+      <c r="I123" s="9">
+        <f>E123*G123</f>
+        <v>1500.0</v>
+      </c>
+      <c r="J123" s="9">
+        <f>H123+I123</f>
+        <v>1500.0</v>
+      </c>
+      <c r="K123" s="10" t="inlineStr">
+        <is>
+          <t>лист 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="C124" s="12" t="inlineStr">
+        <is>
+          <t>Итого по разделу</t>
+        </is>
+      </c>
+      <c r="H124" s="13">
+        <f>SUM(H110:H123)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I124" s="13">
+        <f>SUM(I110:I123)</f>
+        <v>21530.0</v>
+      </c>
+      <c r="J124" s="13">
+        <f>SUM(J110:J123)</f>
+        <v>21530.0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="C127" s="12" t="inlineStr">
         <is>
           <t>Итого прямые затраты</t>
         </is>
       </c>
-      <c r="H92" s="14">
-        <f>H12+H20+H29+H42+H49+H60+H69+H83+H89</f>
-        <v>42031.2978</v>
-      </c>
-      <c r="I92" s="14">
-        <f>I12+I20+I29+I42+I49+I60+I69+I83+I89</f>
-        <v>23240.947</v>
-      </c>
-      <c r="J92" s="13">
-        <f>H92+I92</f>
-        <v>65272.2448</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="C93" s="15" t="inlineStr">
+      <c r="H127" s="14">
+        <f>H12+H20+H29+H42+H49+H60+H69+H83+H92+H101+H107+H124</f>
+        <v>43687.4478</v>
+      </c>
+      <c r="I127" s="14">
+        <f>I12+I20+I29+I42+I49+I60+I69+I83+I92+I101+I107+I124</f>
+        <v>45876.209</v>
+      </c>
+      <c r="J127" s="13">
+        <f>H127+I127</f>
+        <v>89563.6568</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="C128" s="15" t="inlineStr">
         <is>
           <t>Запас на материалы</t>
         </is>
       </c>
-      <c r="I93" s="16">
-        <f>I92*Параметры!$B$4</f>
-        <v>2324.0947</v>
-      </c>
-      <c r="J93" s="17">
-        <f>I93</f>
-        <v>2324.0947</v>
-      </c>
-      <c r="K93" s="2" t="inlineStr">
-        <is>
-          <t>параметр; в LVT запас уже учтён</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="C94" s="15" t="inlineStr">
+      <c r="I128" s="16">
+        <f>(I127-I124)*Параметры!$B$4</f>
+        <v>2434.6209</v>
+      </c>
+      <c r="J128" s="17">
+        <f>I128</f>
+        <v>2434.6209</v>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>параметр; без раздела 12 и LVT (запас уже в цене)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="C129" s="15" t="inlineStr">
         <is>
           <t>Накладные и прибыль подрядчика</t>
         </is>
       </c>
-      <c r="H94" s="16">
-        <f>H92*Параметры!$B$7</f>
-        <v>8406.25956</v>
-      </c>
-      <c r="J94" s="17">
-        <f>H94</f>
-        <v>8406.25956</v>
-      </c>
-      <c r="K94" s="2" t="inlineStr">
+      <c r="H129" s="16">
+        <f>H127*Параметры!$B$7</f>
+        <v>8737.48956</v>
+      </c>
+      <c r="J129" s="17">
+        <f>H129</f>
+        <v>8737.48956</v>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
         <is>
           <t>параметр</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="C95" s="15" t="inlineStr">
+    <row r="130">
+      <c r="C130" s="15" t="inlineStr">
         <is>
           <t>Доставка и подъём материалов</t>
         </is>
       </c>
-      <c r="I95" s="16">
+      <c r="I130" s="16">
         <f>Параметры!$B$8</f>
         <v>500.0</v>
       </c>
-      <c r="J95" s="17">
-        <f>I95</f>
+      <c r="J130" s="17">
+        <f>I130</f>
         <v>500.0</v>
       </c>
-      <c r="K95" s="2" t="inlineStr">
+      <c r="K130" s="2" t="inlineStr">
         <is>
           <t>параметр</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="C96" s="15" t="inlineStr">
+    <row r="131">
+      <c r="C131" s="15" t="inlineStr">
         <is>
           <t>Непредвиденные</t>
         </is>
       </c>
-      <c r="J96" s="17">
-        <f>(J92+J93+J94+J95)*Параметры!$B$6</f>
-        <v>3825.129953</v>
-      </c>
-      <c r="K96" s="2" t="inlineStr">
-        <is>
-          <t>параметр</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="C97" s="18" t="inlineStr">
+      <c r="J131" s="17">
+        <f>(J127-J124+J128+J129+J130)*Параметры!$B$6</f>
+        <v>3985.288363</v>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>параметр; на работы и материалы без раздела 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="C132" s="18" t="inlineStr">
         <is>
           <t>ИТОГО К ОПЛАТЕ, BYN</t>
         </is>
       </c>
-      <c r="H97" s="14">
-        <f>H92+H94</f>
-        <v>50437.55736</v>
-      </c>
-      <c r="I97" s="14">
-        <f>I92+I93+I95</f>
-        <v>26065.0417</v>
-      </c>
-      <c r="J97" s="19">
-        <f>J92+J93+J94+J95+J96</f>
-        <v>80327.729013</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="C98" s="15" t="inlineStr">
+      <c r="H132" s="14">
+        <f>H127+H129</f>
+        <v>52424.93736</v>
+      </c>
+      <c r="I132" s="14">
+        <f>I127+I128+I130</f>
+        <v>48810.8299</v>
+      </c>
+      <c r="J132" s="19">
+        <f>J127+J128+J129+J130+J131</f>
+        <v>105221.055623</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="C133" s="15" t="inlineStr">
         <is>
           <t>Справочно: эквивалент в €</t>
         </is>
       </c>
-      <c r="J98" s="17">
-        <f>J97/Параметры!$B$3</f>
-        <v>23292.1764760634</v>
-      </c>
-      <c r="K98" s="2" t="inlineStr">
+      <c r="J133" s="17">
+        <f>J132/Параметры!$B$3</f>
+        <v>30510.3533572071</v>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
         <is>
           <t>валютная оговорка договора, ст. 298 ГК</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="C99" s="15" t="inlineStr">
-        <is>
-          <t>Справочно: на м² без балкона, BYN</t>
-        </is>
-      </c>
-      <c r="J99" s="17">
-        <f>J97/Объёмы!$B$9</f>
-        <v>1490.8635674276</v>
-      </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>рынок: новостройка с материалами 700–1 100; дизайнерский 1 500–1 800</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="C100" s="15" t="inlineStr">
+    <row r="134">
+      <c r="C134" s="15" t="inlineStr">
+        <is>
+          <t>Справочно: на м² без балкона, BYN (всё включено)</t>
+        </is>
+      </c>
+      <c r="J134" s="17">
+        <f>J132/Объёмы!$B$9</f>
+        <v>1952.8777955271</v>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>рынок: дизайнерский ремонт всё включено 1 500–1 800</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="C135" s="15" t="inlineStr">
+        <is>
+          <t>Справочно: на м² без приборов и изделий раздела 12, BYN</t>
+        </is>
+      </c>
+      <c r="J135" s="17">
+        <f>(J132-J124)/Объёмы!$B$9</f>
+        <v>1553.2861103007</v>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>ремонт с черновыми и отделочными материалами, без сантехприборов, света и дверей</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="C136" s="15" t="inlineStr">
         <is>
           <t>Справочно: только работы на м², BYN</t>
         </is>
       </c>
-      <c r="J100" s="17">
-        <f>H97/Объёмы!$B$9</f>
-        <v>936.1090824053</v>
-      </c>
-      <c r="K100" s="2" t="inlineStr">
+      <c r="J136" s="17">
+        <f>H132/Объёмы!$B$9</f>
+        <v>972.9943830735</v>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
         <is>
           <t>рынок: новостройка «с нуля» работа 440–600, дизайнерский 730–1 000</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="C101" s="15" t="inlineStr">
+    <row r="137">
+      <c r="C137" s="15" t="inlineStr">
         <is>
           <t>Справочно: доля работ в итоге</t>
         </is>
       </c>
-      <c r="J101" s="20">
-        <f>H97/J97</f>
-        <v>0.6278972153</v>
-      </c>
-    </row>
-    <row r="103" ht="28" customHeight="1">
-      <c r="C103" s="21" t="inlineStr">
-        <is>
-          <t>НЕ ВКЛЮЧЕНО (закупка заказчика по спецификации листов 26–27): сантехприборы и смесители MOZA/TECE/Roca/Kaldewei/Сунержа, светильники и споты (44 + подвесы), двери с коробками (3 межкомнатных + входная), радиаторы Royal Thermo, розетки серии Vertus сверх ~12 руб./шт, кухня и корпусная мебель, столешница и фартук Coverlam, шторы и профили Laconistiq/Loconistic, зеркала.</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="28" customHeight="1">
-      <c r="C104" s="21" t="inlineStr">
+      <c r="J137" s="20">
+        <f>H132/J132</f>
+        <v>0.4982361852</v>
+      </c>
+    </row>
+    <row r="139" ht="28" customHeight="1">
+      <c r="C139" s="21" t="inlineStr">
+        <is>
+          <t>НЕ ВКЛЮЧЕНО: кухня и корпусная мебель, столешница и фартук Coverlam, бытовая техника, шторы и карнизные профили Laconistiq/Loconistic, замена остекления балкона на тёплое (если стоит холодное — 2 500–4 000 руб. за витраж 3,5 м). Раздел 12 — ориентировочные цены приборов и изделий по спецификации проекта (±20–30 %), заменить на счета салонов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="28" customHeight="1">
+      <c r="C140" s="21" t="inlineStr">
         <is>
           <t>Чистовые материалы в строках M19, M20, M21, M32–M35 — ориентировочные розничные цены; заменить на счета салонов (alexparket, terracotta, premiumdecor, minskoboi, vinni).</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="28" customHeight="1">
-      <c r="C105" s="21" t="inlineStr">
+    <row r="141" ht="28" customHeight="1">
+      <c r="C141" s="21" t="inlineStr">
+        <is>
+          <t>Балкон утеплён изнутри как жилое помещение (винил, обои, натяжной потолок по проекту): ЭППС 50 мм, пароизоляция, ГКЛВ, стяжка до уровня квартиры. Тёплый пол на балконе исключён.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="28" customHeight="1">
+      <c r="C142" s="21" t="inlineStr">
+        <is>
+          <t>Вентиляция: 4 точки — естественная решётка на кухне, воздуховод вытяжки, вентилятор зоны стиральной машины, вентилятор санузла; выводы электрики к ним учтены в разделе 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="28" customHeight="1">
+      <c r="C143" s="21" t="inlineStr">
         <is>
           <t>Микроцемент (M37–M38) — фикс студии UNICORE до 20 м² стен по CLAUDE.md; при изменении площади пересчитать по модели costs.py.</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="28" customHeight="1">
-      <c r="C106" s="21" t="inlineStr">
+    <row r="144" ht="28" customHeight="1">
+      <c r="C144" s="21" t="inlineStr">
         <is>
           <t>Тёплый пол на балконе (2,2 м²) исключён: проект (лист 13 п. 8) сам отмечает незаконность; присоединение балкона запрещено пост. № 164 п. 4.</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="28" customHeight="1">
-      <c r="C107" s="21" t="inlineStr">
+    <row r="145" ht="28" customHeight="1">
+      <c r="C145" s="21" t="inlineStr">
         <is>
           <t>Штукатурка только новых перегородок; существующие стены — шпаклёвка по факту плоскости (класс «улучшенная», ≤ 2 мм/м). Если замер покажет отклонения &gt; 8 мм на высоту — добавить строку локального выравнивания.</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="28" customHeight="1">
-      <c r="C108" s="21" t="inlineStr">
+    <row r="146" ht="28" customHeight="1">
+      <c r="C146" s="21" t="inlineStr">
         <is>
           <t>Перепланировка (новые перегородки, проёмы, гидроизоляция) требует согласования администрации района по пост. № 164 п. 7 без проекта; срок до 1 месяца. Шумные работы — рабочие дни 9:00–19:00.</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="28" customHeight="1">
-      <c r="C109" s="21" t="inlineStr">
+    <row r="147" ht="28" customHeight="1">
+      <c r="C147" s="21" t="inlineStr">
         <is>
           <t>Гарантия на пол — только при протоколе влажности основания CM ≤ 2,0 % и ровности ≤ 2 мм/2 м после самонивелира (акт скрытых работ).</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="28" customHeight="1">
-      <c r="C110" s="21" t="inlineStr">
+    <row r="148" ht="28" customHeight="1">
+      <c r="C148" s="21" t="inlineStr">
         <is>
           <t>Итог может отличаться на ±10 % после обмера по факту (допуск проекта 20 мм) и выбора материалов; смета приблизительная в смысле ст. 663 ГК — превышение согласовывать письменно.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="C108:K108"/>
-    <mergeCell ref="C103:K103"/>
-    <mergeCell ref="C104:K104"/>
-    <mergeCell ref="C107:K107"/>
-    <mergeCell ref="C110:K110"/>
-    <mergeCell ref="C106:K106"/>
-    <mergeCell ref="C105:K105"/>
-    <mergeCell ref="C109:K109"/>
+  <mergeCells count="10">
+    <mergeCell ref="C143:K143"/>
+    <mergeCell ref="C146:K146"/>
+    <mergeCell ref="C141:K141"/>
+    <mergeCell ref="C148:K148"/>
+    <mergeCell ref="C142:K142"/>
+    <mergeCell ref="C140:K140"/>
+    <mergeCell ref="C144:K144"/>
+    <mergeCell ref="C145:K145"/>
+    <mergeCell ref="C147:K147"/>
+    <mergeCell ref="C139:K139"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9283,7 +10613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11422,8 +12752,968 @@
       </c>
       <c r="H59" s="2" t="inlineStr"/>
     </row>
+    <row r="60">
+      <c r="A60" s="15" t="inlineStr">
+        <is>
+          <t>B01</t>
+        </is>
+      </c>
+      <c r="B60" s="15" t="inlineStr">
+        <is>
+          <t>Утепление парапета и боковых стен балкона ЭППС 50 мм на клей-пену с дюбелями, швы пеной</t>
+        </is>
+      </c>
+      <c r="C60" s="15" t="inlineStr">
+        <is>
+          <t>м²</t>
+        </is>
+      </c>
+      <c r="D60" s="21" t="inlineStr">
+        <is>
+          <t>ЭППС Технониколь Carbon 50 мм ≈ 11/м² + клей-пена 4 + дюбели-грибки 1</t>
+        </is>
+      </c>
+      <c r="E60" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>ввод</t>
+        </is>
+      </c>
+      <c r="G60" s="23" t="n">
+        <v>25</v>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>оценка по нормам утепления</t>
+        </is>
+      </c>
+    </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="A61" s="15" t="inlineStr">
+        <is>
+          <t>B02</t>
+        </is>
+      </c>
+      <c r="B61" s="15" t="inlineStr">
+        <is>
+          <t>Пароизоляция фольгированная (пенофол 5 мм) с проклейкой швов, стены и потолок балкона</t>
+        </is>
+      </c>
+      <c r="C61" s="15" t="inlineStr">
+        <is>
+          <t>м²</t>
+        </is>
+      </c>
+      <c r="D61" s="21" t="inlineStr">
+        <is>
+          <t>пенофол ≈ 6/м² + алюминиевый скотч 1</t>
+        </is>
+      </c>
+      <c r="E61" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>ввод</t>
+        </is>
+      </c>
+      <c r="G61" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="15" t="inlineStr">
+        <is>
+          <t>B03</t>
+        </is>
+      </c>
+      <c r="B62" s="15" t="inlineStr">
+        <is>
+          <t>Каркас и обшивка ГКЛВ парапета и боковых стен балкона (под обои ОБ-1)</t>
+        </is>
+      </c>
+      <c r="C62" s="15" t="inlineStr">
+        <is>
+          <t>м²</t>
+        </is>
+      </c>
+      <c r="D62" s="21" t="inlineStr">
+        <is>
+          <t>ГКЛВ 12,5 6,5 + профиль ПП/ПН 2 м × 3 + подвесы, саморезы 2</t>
+        </is>
+      </c>
+      <c r="E62" s="23" t="n">
+        <v>15</v>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>ввод</t>
+        </is>
+      </c>
+      <c r="G62" s="23" t="n">
+        <v>45</v>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>ставка облицовки стен ГКЛ по каркасу</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="15" t="inlineStr">
+        <is>
+          <t>B04</t>
+        </is>
+      </c>
+      <c r="B63" s="15" t="inlineStr">
+        <is>
+          <t>Утепление потолка балкона ЭППС 50 мм + пароизоляция (под натяжной потолок)</t>
+        </is>
+      </c>
+      <c r="C63" s="15" t="inlineStr">
+        <is>
+          <t>м²</t>
+        </is>
+      </c>
+      <c r="D63" s="21" t="inlineStr">
+        <is>
+          <t>ЭППС 11 + клей-пена 4 + грибки 1 + пенофол 7</t>
+        </is>
+      </c>
+      <c r="E63" s="23" t="n">
+        <v>23</v>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>ввод</t>
+        </is>
+      </c>
+      <c r="G63" s="23" t="n">
+        <v>30</v>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="15" t="inlineStr">
+        <is>
+          <t>B05</t>
+        </is>
+      </c>
+      <c r="B64" s="15" t="inlineStr">
+        <is>
+          <t>Пол балкона: ЭППС 50 мм, плёнка, стяжка ЦПС 50 мм с сеткой до уровня квартиры</t>
+        </is>
+      </c>
+      <c r="C64" s="15" t="inlineStr">
+        <is>
+          <t>м²</t>
+        </is>
+      </c>
+      <c r="D64" s="21" t="inlineStr">
+        <is>
+          <t>ЭППС 11 + плёнка 1 + ЦПС 100 кг × 0,35 + сетка 3 + демпфер 1</t>
+        </is>
+      </c>
+      <c r="E64" s="23" t="n">
+        <v>51</v>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>ввод</t>
+        </is>
+      </c>
+      <c r="G64" s="23" t="n">
+        <v>40</v>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>утепление 15 + стяжка 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="15" t="inlineStr">
+        <is>
+          <t>B06</t>
+        </is>
+      </c>
+      <c r="B65" s="15" t="inlineStr">
+        <is>
+          <t>Герметизация примыканий остекления и балконного блока: пена, герметик, откосы</t>
+        </is>
+      </c>
+      <c r="C65" s="15" t="inlineStr">
+        <is>
+          <t>м.п.</t>
+        </is>
+      </c>
+      <c r="D65" s="21" t="inlineStr">
+        <is>
+          <t>пена, ПСУЛ, герметик ≈ 5/м.п.</t>
+        </is>
+      </c>
+      <c r="E65" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>ввод</t>
+        </is>
+      </c>
+      <c r="G65" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="15" t="inlineStr">
+        <is>
+          <t>V01</t>
+        </is>
+      </c>
+      <c r="B66" s="15" t="inlineStr">
+        <is>
+          <t>Кухня: приточно-вытяжная решётка с клапаном в существующий вентканал</t>
+        </is>
+      </c>
+      <c r="C66" s="15" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D66" s="21" t="inlineStr">
+        <is>
+          <t>решётка с обратным клапаном ≈ 25</t>
+        </is>
+      </c>
+      <c r="E66" s="23" t="n">
+        <v>25</v>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>ввод</t>
+        </is>
+      </c>
+      <c r="G66" s="23" t="n">
+        <v>30</v>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="15" t="inlineStr">
+        <is>
+          <t>V02</t>
+        </is>
+      </c>
+      <c r="B67" s="15" t="inlineStr">
+        <is>
+          <t>Кухонная вытяжка: воздуховод ПВХ 125 (≈3 м) с обратным клапаном к вентканалу, скрыто за кухней</t>
+        </is>
+      </c>
+      <c r="C67" s="15" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D67" s="21" t="inlineStr">
+        <is>
+          <t>воздуховод 3 × 12 + клапан 25 + переходники, решётка 20</t>
+        </is>
+      </c>
+      <c r="E67" s="23" t="n">
+        <v>80</v>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>ввод</t>
+        </is>
+      </c>
+      <c r="G67" s="23" t="n">
+        <v>120</v>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>монтаж воздуховода + подключение вытяжки</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="15" t="inlineStr">
+        <is>
+          <t>V03</t>
+        </is>
+      </c>
+      <c r="B68" s="15" t="inlineStr">
+        <is>
+          <t>Зона стиральной машины: накладной/канальный вентилятор 100 мм с обратным клапаном и воздуховодом</t>
+        </is>
+      </c>
+      <c r="C68" s="15" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D68" s="21" t="inlineStr">
+        <is>
+          <t>вентилятор ≈ 80 + воздуховод 2 м 25</t>
+        </is>
+      </c>
+      <c r="E68" s="23" t="n">
+        <v>105</v>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>ввод</t>
+        </is>
+      </c>
+      <c r="G68" s="23" t="n">
+        <v>90</v>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="15" t="inlineStr">
+        <is>
+          <t>V04</t>
+        </is>
+      </c>
+      <c r="B69" s="15" t="inlineStr">
+        <is>
+          <t>Санузел: вентилятор 100 мм с таймером и обратным клапаном под скрытую решётку</t>
+        </is>
+      </c>
+      <c r="C69" s="15" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D69" s="21" t="inlineStr">
+        <is>
+          <t>вентилятор с таймером ≈ 110</t>
+        </is>
+      </c>
+      <c r="E69" s="23" t="n">
+        <v>110</v>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>ввод</t>
+        </is>
+      </c>
+      <c r="G69" s="23" t="n">
+        <v>60</v>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>закладная под решётку — в потолках</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="15" t="inlineStr">
+        <is>
+          <t>H01</t>
+        </is>
+      </c>
+      <c r="B70" s="15" t="inlineStr">
+        <is>
+          <t>Закладные под подвесную мебель, тумбу умывальника, зеркала, полки (фанера/брус в перегородках)</t>
+        </is>
+      </c>
+      <c r="C70" s="15" t="inlineStr">
+        <is>
+          <t>компл</t>
+        </is>
+      </c>
+      <c r="D70" s="21" t="inlineStr">
+        <is>
+          <t>лист 4 п. 10; фанера 18 мм 0,5 листа + брус</t>
+        </is>
+      </c>
+      <c r="E70" s="23" t="n">
+        <v>60</v>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>ввод</t>
+        </is>
+      </c>
+      <c r="G70" s="23" t="n">
+        <v>150</v>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="15" t="inlineStr">
+        <is>
+          <t>H02</t>
+        </is>
+      </c>
+      <c r="B71" s="15" t="inlineStr">
+        <is>
+          <t>Заделка отверстий и штроб после демонтажа радиаторов, щитка, старых выводов</t>
+        </is>
+      </c>
+      <c r="C71" s="15" t="inlineStr">
+        <is>
+          <t>компл</t>
+        </is>
+      </c>
+      <c r="D71" s="21" t="inlineStr">
+        <is>
+          <t>ремсостав, пена</t>
+        </is>
+      </c>
+      <c r="E71" s="23" t="n">
+        <v>30</v>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>ввод</t>
+        </is>
+      </c>
+      <c r="G71" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="15" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B72" s="15" t="inlineStr">
+        <is>
+          <t>Инсталляция TECE + унитаз Roca The Gap Clean Rim с крышкой SoftClose + клавиша</t>
+        </is>
+      </c>
+      <c r="C72" s="15" t="inlineStr">
+        <is>
+          <t>компл</t>
+        </is>
+      </c>
+      <c r="D72" s="21" t="inlineStr">
+        <is>
+          <t>TECE base ≈ 850 + Roca 34647L ≈ 700 + клавиша 150</t>
+        </is>
+      </c>
+      <c r="E72" s="23" t="n">
+        <v>1700</v>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>ввод</t>
+        </is>
+      </c>
+      <c r="G72" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>оценка ±20 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="15" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B73" s="15" t="inlineStr">
+        <is>
+          <t>Ванна стальная Kaldewei Eurowa 170×70 с ножками и шумоизоляцией</t>
+        </is>
+      </c>
+      <c r="C73" s="15" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D73" s="21" t="inlineStr"/>
+      <c r="E73" s="23" t="n">
+        <v>900</v>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>ввод</t>
+        </is>
+      </c>
+      <c r="G73" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="15" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B74" s="15" t="inlineStr">
+        <is>
+          <t>Полотенцесушитель Сунержа Богема 3.1 800×500 электрический (МЭМ)</t>
+        </is>
+      </c>
+      <c r="C74" s="15" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D74" s="21" t="inlineStr"/>
+      <c r="E74" s="23" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>ввод</t>
+        </is>
+      </c>
+      <c r="G74" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="15" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B75" s="15" t="inlineStr">
+        <is>
+          <t>Умывальник литой под заказ</t>
+        </is>
+      </c>
+      <c r="C75" s="15" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D75" s="21" t="inlineStr">
+        <is>
+          <t>лист 26</t>
+        </is>
+      </c>
+      <c r="E75" s="23" t="n">
+        <v>800</v>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>ввод</t>
+        </is>
+      </c>
+      <c r="G75" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="15" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B76" s="15" t="inlineStr">
+        <is>
+          <t>Скрытые смесители MOZA 316L: раковина и гигиенический душ (биде)</t>
+        </is>
+      </c>
+      <c r="C76" s="15" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D76" s="21" t="inlineStr"/>
+      <c r="E76" s="23" t="n">
+        <v>550</v>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>ввод</t>
+        </is>
+      </c>
+      <c r="G76" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="15" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B77" s="15" t="inlineStr">
+        <is>
+          <t>Душевая система MOZA 316L со скрытым сливом, смеситель на 3 отверстия, 2 режима</t>
+        </is>
+      </c>
+      <c r="C77" s="15" t="inlineStr">
+        <is>
+          <t>компл</t>
+        </is>
+      </c>
+      <c r="D77" s="21" t="inlineStr"/>
+      <c r="E77" s="23" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>ввод</t>
+        </is>
+      </c>
+      <c r="G77" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="15" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="B78" s="15" t="inlineStr">
+        <is>
+          <t>Смеситель кухонный Vieir V15019-L под фильтр + дозатор Paulmark</t>
+        </is>
+      </c>
+      <c r="C78" s="15" t="inlineStr">
+        <is>
+          <t>компл</t>
+        </is>
+      </c>
+      <c r="D78" s="21" t="inlineStr"/>
+      <c r="E78" s="23" t="n">
+        <v>330</v>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>ввод</t>
+        </is>
+      </c>
+      <c r="G78" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="15" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B79" s="15" t="inlineStr">
+        <is>
+          <t>Проточный водонагреватель</t>
+        </is>
+      </c>
+      <c r="C79" s="15" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D79" s="21" t="inlineStr">
+        <is>
+          <t>лист 9: вывод в шкафу</t>
+        </is>
+      </c>
+      <c r="E79" s="23" t="n">
+        <v>350</v>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>ввод</t>
+        </is>
+      </c>
+      <c r="G79" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="15" t="inlineStr">
+        <is>
+          <t>P09</t>
+        </is>
+      </c>
+      <c r="B80" s="15" t="inlineStr">
+        <is>
+          <t>Зеркало с подсветкой (санузел) и зеркало (прихожая)</t>
+        </is>
+      </c>
+      <c r="C80" s="15" t="inlineStr">
+        <is>
+          <t>компл</t>
+        </is>
+      </c>
+      <c r="D80" s="21" t="inlineStr">
+        <is>
+          <t>zerkala.minsk</t>
+        </is>
+      </c>
+      <c r="E80" s="23" t="n">
+        <v>800</v>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>ввод</t>
+        </is>
+      </c>
+      <c r="G80" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="15" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="B81" s="15" t="inlineStr">
+        <is>
+          <t>Радиатор стальной трубчатый Royal Thermo Insignia VC2180, 8 секций, RAL 9016</t>
+        </is>
+      </c>
+      <c r="C81" s="15" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D81" s="21" t="inlineStr">
+        <is>
+          <t>лист 4</t>
+        </is>
+      </c>
+      <c r="E81" s="23" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>ввод</t>
+        </is>
+      </c>
+      <c r="G81" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="15" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="B82" s="15" t="inlineStr">
+        <is>
+          <t>Двери межкомнатные с коробкой, наличниками и фурнитурой (homeporte.by)</t>
+        </is>
+      </c>
+      <c r="C82" s="15" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D82" s="21" t="inlineStr">
+        <is>
+          <t>ДВ-1 700, ДВ-2 800 ×2</t>
+        </is>
+      </c>
+      <c r="E82" s="23" t="n">
+        <v>750</v>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>ввод</t>
+        </is>
+      </c>
+      <c r="G82" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="15" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="B83" s="15" t="inlineStr">
+        <is>
+          <t>Входная дверь (joinery.by)</t>
+        </is>
+      </c>
+      <c r="C83" s="15" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D83" s="21" t="inlineStr"/>
+      <c r="E83" s="23" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>ввод</t>
+        </is>
+      </c>
+      <c r="G83" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="15" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+      <c r="B84" s="15" t="inlineStr">
+        <is>
+          <t>Светильники по спецификации листа 10: 44 спота GU10, 5 подвесных, потолочный, трек Flexy 3 м + 4 светильника, скрытая решётка</t>
+        </is>
+      </c>
+      <c r="C84" s="15" t="inlineStr">
+        <is>
+          <t>компл</t>
+        </is>
+      </c>
+      <c r="D84" s="21" t="inlineStr">
+        <is>
+          <t>44 × 35 + Flamingo-аналог 600 + Cisterna 300 + Jemstone 6 × 150 + Caspian 450 + потолочный 150 + трек 700 + решётка 60</t>
+        </is>
+      </c>
+      <c r="E84" s="23" t="n">
+        <v>4700</v>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>ввод</t>
+        </is>
+      </c>
+      <c r="G84" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>оценка; оригиналы Vibia/Romatti дороже в разы</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="15" t="inlineStr">
+        <is>
+          <t>P14</t>
+        </is>
+      </c>
+      <c r="B85" s="15" t="inlineStr">
+        <is>
+          <t>Розетки и выключатели серии Vertus сверх учтённых 12 руб./механизм</t>
+        </is>
+      </c>
+      <c r="C85" s="15" t="inlineStr">
+        <is>
+          <t>компл</t>
+        </is>
+      </c>
+      <c r="D85" s="21" t="inlineStr">
+        <is>
+          <t>~120 механизмов × (25 − 12)</t>
+        </is>
+      </c>
+      <c r="E85" s="23" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>ввод</t>
+        </is>
+      </c>
+      <c r="G85" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>Материал — розница Минска 27.09.2026 по расходу из техкарт, без запаса. Чистовые материалы заказчика (плитка, LVT, обои, Marmorino) — ориентировочные цены, помечены «оценка»; заменить на счета поставщиков.</t>
         </is>
@@ -11440,7 +13730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="64" customWidth="1" min="1" max="1"/>
@@ -12254,6 +14544,131 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>Балкон: парапет и боковые стены под утепление</t>
+        </is>
+      </c>
+      <c r="B41" s="16">
+        <f>3.52*1.0+2*1.26*2.7</f>
+        <v>10.324</v>
+      </c>
+      <c r="C41" s="15" t="inlineStr">
+        <is>
+          <t>м²</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>лист 2/14/17: длина 3,52, глубина 1,26; парапет h≈1,0 + две торцевые стены</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>Балкон: потолок</t>
+        </is>
+      </c>
+      <c r="B42" s="16">
+        <f>B8</f>
+        <v>3.15</v>
+      </c>
+      <c r="C42" s="15" t="inlineStr">
+        <is>
+          <t>м²</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>экспликация</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="15" t="inlineStr">
+        <is>
+          <t>Балкон: пол</t>
+        </is>
+      </c>
+      <c r="B43" s="16">
+        <f>B8</f>
+        <v>3.15</v>
+      </c>
+      <c r="C43" s="15" t="inlineStr">
+        <is>
+          <t>м²</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>экспликация</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>Балкон: пароизоляция стены + потолок</t>
+        </is>
+      </c>
+      <c r="B44" s="16">
+        <f>B41+B42</f>
+        <v>13.474</v>
+      </c>
+      <c r="C44" s="15" t="inlineStr">
+        <is>
+          <t>м²</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>расчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>Балкон: примыкания остекления и блока</t>
+        </is>
+      </c>
+      <c r="B45" s="16">
+        <f>3.52+2*1.26+3.52</f>
+        <v>9.56</v>
+      </c>
+      <c r="C45" s="15" t="inlineStr">
+        <is>
+          <t>м.п.</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>верх и низ остекления, торцы</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="15" t="inlineStr">
+        <is>
+          <t>Вентиляция, точек</t>
+        </is>
+      </c>
+      <c r="B46" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C46" s="15" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>по заданию заказчика: кухня естественная, вытяжка, стиральная, санузел</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
